--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -501,32 +501,32 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.8</v>
+        <v>20.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="H2" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K2" t="n">
         <v>3.4</v>
@@ -544,35 +544,35 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.2</v>
+        <v>20.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G3" t="n">
         <v>6.3</v>
       </c>
       <c r="H3" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="4">
@@ -583,39 +583,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.7</v>
+        <v>21.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="H4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.7</v>
+        <v>22</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>2.6</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.6</v>
+        <v>22.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
         <v>5.6</v>
       </c>
       <c r="H6" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="7">
@@ -712,7 +712,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -720,31 +720,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
       <c r="G7" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="H7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -755,39 +755,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.9</v>
+        <v>23.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="H8" t="n">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="K8" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="9">
@@ -798,30 +798,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.9</v>
+        <v>21.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="H9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I9" t="n">
         <v>2.2</v>
@@ -830,7 +830,7 @@
         <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="10">
@@ -841,36 +841,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24.7</v>
+        <v>23.5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="H10" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
         <v>3.2</v>
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>23.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="H11" t="n">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="12">
@@ -931,35 +931,35 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
         <v>5.4</v>
       </c>
       <c r="H12" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>0.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13">
@@ -970,36 +970,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24.1</v>
+        <v>25.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.8</v>
       </c>
       <c r="G13" t="n">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="H13" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="K13" t="n">
         <v>3.7</v>
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.6</v>
+        <v>23.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
         <v>6.5</v>
       </c>
       <c r="H14" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.4</v>
+        <v>24.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>2.7</v>
       </c>
       <c r="G15" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="16">
@@ -1099,36 +1099,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26.1</v>
+        <v>28.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K16" t="n">
         <v>3.4</v>
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2.8</v>
       </c>
       <c r="G17" t="n">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
       <c r="H17" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.4</v>
+        <v>24.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="H18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.9</v>
+        <v>26.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="H19" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>27.8</v>
+        <v>26.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="H20" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="21">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>25.1</v>
+        <v>23.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3.2</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="H21" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="K21" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="22">
@@ -1361,35 +1361,35 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="n">
         <v>4.5</v>
       </c>
       <c r="H22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I22" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.5</v>
+        <v>24.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="G23" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H23" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
         <v>0.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="24">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.3</v>
+        <v>22.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H24" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -1486,36 +1486,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.6</v>
+        <v>24.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="G25" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H25" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="K25" t="n">
         <v>2.9</v>
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>26.7</v>
+        <v>25.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="H26" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="I26" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="27">
@@ -1576,35 +1576,35 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>27.2</v>
+        <v>25.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H27" t="n">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I27" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
         <v>0.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="G28" t="n">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="H28" t="n">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="I28" t="n">
         <v>2.2</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K28" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="29">
@@ -1658,36 +1658,36 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="G29" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="H29" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K29" t="n">
         <v>3.2</v>
@@ -1701,39 +1701,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.9</v>
+        <v>26.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K30" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="31">
@@ -1748,35 +1748,35 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="I31" t="n">
         <v>2.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K31" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
@@ -1858,39 +1858,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G2" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I2" t="n">
         <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3">
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1924,16 +1924,16 @@
         <v>5.5</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="4">
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.3</v>
+        <v>22.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>22.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="H6" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="7">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.4</v>
+        <v>24.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G7" t="n">
-        <v>6.7</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
         <v>0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -2116,11 +2116,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.9</v>
+        <v>22.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2129,26 +2129,26 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2167,31 +2167,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="G9" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="H9" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.5</v>
+        <v>23.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K10" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="H11" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
         <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.1</v>
+        <v>24.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="G12" t="n">
-        <v>5.1</v>
+        <v>6.9</v>
       </c>
       <c r="H12" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="H13" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="H14" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25.2</v>
+        <v>23.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G16" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="17">
@@ -2507,35 +2507,35 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.8</v>
+        <v>23.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G17" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
         <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>24.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="G18" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H18" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -2589,11 +2589,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.4</v>
+        <v>22.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,26 +2602,26 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>8.300000000000001</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I19" t="n">
         <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -2632,36 +2632,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>25.1</v>
+        <v>23.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="G20" t="n">
         <v>6.4</v>
       </c>
       <c r="H20" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K20" t="n">
         <v>2.5</v>
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H21" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.2</v>
+        <v>24.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
       <c r="H22" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23">
@@ -2765,35 +2765,35 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G23" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="H23" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="24">
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.4</v>
+        <v>25.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2817,26 +2817,26 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G24" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="H24" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K24" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H25" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>26</v>
+        <v>24.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G26" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="27">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>4.1</v>
       </c>
       <c r="G27" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H27" t="n">
         <v>5.8</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="28">
@@ -2980,35 +2980,35 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25.8</v>
+        <v>25.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G28" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="H28" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -3019,39 +3019,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25.2</v>
+        <v>26.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G29" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="H29" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K29" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -3062,39 +3062,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.8</v>
+        <v>25</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="G30" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="H30" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -3105,39 +3105,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>27.3</v>
+        <v>25.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="G31" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="H31" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K31" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
@@ -3223,35 +3223,35 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23.9</v>
+        <v>23.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H2" t="n">
         <v>3.8</v>
       </c>
-      <c r="G2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4.1</v>
-      </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J2" t="n">
         <v>0.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -3262,39 +3262,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.2</v>
+        <v>22.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
         <v>1.3</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
@@ -3305,39 +3305,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.1</v>
+        <v>21.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5">
@@ -3352,11 +3352,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19.7</v>
+        <v>20.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3365,19 +3365,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K5" t="n">
         <v>2.8</v>
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>22.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.3</v>
+        <v>21.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>20.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" t="n">
         <v>2.8</v>
-      </c>
-      <c r="G8" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.1</v>
       </c>
     </row>
     <row r="9">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.7</v>
+        <v>20</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G9" t="n">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
         <v>0.8</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.3</v>
+        <v>21.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>8.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>22.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.8</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.7</v>
+        <v>22.9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.2</v>
+        <v>22.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
         <v>7.2</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.9</v>
+        <v>21.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="17">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2.5</v>
       </c>
       <c r="G17" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="H17" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18">
@@ -3907,36 +3907,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="G18" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="H18" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="I18" t="n">
         <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.9</v>
+        <v>22.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
         <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="21">
@@ -4036,39 +4036,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.6</v>
+        <v>24.3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.9</v>
+        <v>22.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G22" t="n">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="H22" t="n">
         <v>4.5</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23">
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.3</v>
+        <v>26.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K23" t="n">
         <v>2.9</v>
-      </c>
-      <c r="G23" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="24">
@@ -4169,32 +4169,32 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>20.6</v>
+        <v>22.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K24" t="n">
         <v>2.4</v>
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.4</v>
+        <v>24.5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="G25" t="n">
-        <v>6.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="26">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G26" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="H26" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K26" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.6</v>
+        <v>24.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G27" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="H27" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -4345,31 +4345,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -4380,39 +4380,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>23.9</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="G29" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H29" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K29" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -4423,39 +4423,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.3</v>
+        <v>23.2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G30" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="H30" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="I30" t="n">
         <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K30" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="31">
@@ -4466,39 +4466,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24</v>
+        <v>25.9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="H31" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K31" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
     </row>
   </sheetData>
@@ -4584,16 +4584,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4603,7 +4603,7 @@
         <v>9.9</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -4612,7 +4612,7 @@
         <v>0.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3">
@@ -4623,39 +4623,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.8</v>
+        <v>20.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.8</v>
+        <v>21.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="G4" t="n">
         <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="5">
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.8</v>
+        <v>20.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.1</v>
+        <v>21.3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="G6" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.1</v>
+        <v>21.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G8" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>9.9</v>
+        <v>10.6</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.3</v>
+        <v>23.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="13">
@@ -5057,26 +5057,26 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.6</v>
+        <v>20.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
         <v>1.7</v>
@@ -5085,7 +5085,7 @@
         <v>0.9</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.9</v>
+        <v>23.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="G14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.6</v>
+        <v>21.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>9.300000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
         <v>1.6</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="16">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.4</v>
+        <v>24.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>10.9</v>
+        <v>12.3</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="17">
@@ -5225,15 +5225,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.6</v>
+        <v>23.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -5242,22 +5242,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G17" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>8.699999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
@@ -5311,36 +5311,36 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.4</v>
+        <v>22.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G19" t="n">
-        <v>12.3</v>
+        <v>10.2</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>2.5</v>
@@ -5358,32 +5358,32 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.7</v>
+        <v>24.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G20" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
         <v>0.9</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="K20" t="n">
         <v>2.7</v>
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>25.8</v>
+        <v>22.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="G21" t="n">
-        <v>12.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>1.2</v>
       </c>
       <c r="K21" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K22" t="n">
         <v>2.4</v>
-      </c>
-      <c r="G22" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26.8</v>
+        <v>23.4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>69.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="G23" t="n">
-        <v>13.1</v>
+        <v>10.5</v>
       </c>
       <c r="H23" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G24" t="n">
-        <v>10.9</v>
+        <v>9.5</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I24" t="n">
         <v>1.4</v>
       </c>
       <c r="J24" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>22.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="H25" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="I25" t="n">
         <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="K25" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G26" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="27">
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.8</v>
+        <v>25.7</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G27" t="n">
-        <v>9.300000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="H27" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28">
@@ -5698,39 +5698,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26.1</v>
+        <v>23.5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G28" t="n">
-        <v>11.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="K28" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="29">
@@ -5741,39 +5741,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.2</v>
+        <v>27.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="G29" t="n">
-        <v>9.4</v>
+        <v>12.3</v>
       </c>
       <c r="H29" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="K29" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="30">
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>28.6</v>
+        <v>26.2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G30" t="n">
         <v>13.1</v>
       </c>
       <c r="H30" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="31">
@@ -5831,16 +5831,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.8</v>
+        <v>25.9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -5853,13 +5853,13 @@
         <v>5.2</v>
       </c>
       <c r="I31" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>1.2</v>
       </c>
       <c r="K31" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>
@@ -5945,35 +5945,35 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.6</v>
+        <v>17.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>13.1</v>
+        <v>13.5</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J2" t="n">
         <v>1.5</v>
       </c>
-      <c r="J2" t="n">
-        <v>1.6</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="3">
@@ -5988,35 +5988,35 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="n">
-        <v>15.2</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="n">
         <v>1.1</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.5</v>
+        <v>19.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G4" t="n">
-        <v>13.3</v>
+        <v>14</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="H5" t="n">
         <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15.2</v>
+        <v>19.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>12.5</v>
+        <v>14.4</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="G7" t="n">
-        <v>13.7</v>
+        <v>12.6</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.6</v>
+        <v>21.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G8" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.5</v>
+        <v>20.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="G9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24.6</v>
+        <v>16.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="G10" t="n">
-        <v>16.2</v>
+        <v>12.8</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
         <v>1.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19.2</v>
+        <v>24.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="n">
-        <v>12.7</v>
+        <v>15.4</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="12">
@@ -6371,36 +6371,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20.8</v>
+        <v>20.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G12" t="n">
-        <v>13.3</v>
+        <v>14.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
         <v>1.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="K12" t="n">
         <v>2.8</v>
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18.7</v>
+        <v>21</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1.4</v>
       </c>
       <c r="G13" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>1.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20.7</v>
+        <v>17.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G14" t="n">
-        <v>13.1</v>
+        <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.1</v>
+        <v>19.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="G15" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.5</v>
+        <v>23.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="G16" t="n">
-        <v>14.9</v>
+        <v>12.9</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G17" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="18">
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20.5</v>
+        <v>21.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G18" t="n">
-        <v>14.3</v>
+        <v>13.5</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
         <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="G19" t="n">
-        <v>11.7</v>
+        <v>14.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I20" t="n">
         <v>1.3</v>
       </c>
-      <c r="G20" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J20" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -6758,11 +6758,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.7</v>
+        <v>23.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -6771,26 +6771,26 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G21" t="n">
-        <v>16.2</v>
+        <v>13.4</v>
       </c>
       <c r="H21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="22">
@@ -6805,35 +6805,35 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.2</v>
+        <v>22.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>1.3</v>
       </c>
       <c r="G22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="H22" t="n">
         <v>4.5</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>1.7</v>
       </c>
       <c r="K22" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.1</v>
+        <v>25.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="G23" t="n">
-        <v>12.7</v>
+        <v>14.2</v>
       </c>
       <c r="H23" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I23" t="n">
         <v>1.5</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.7</v>
+        <v>24</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="G24" t="n">
-        <v>17</v>
+        <v>11.6</v>
       </c>
       <c r="H24" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="G25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="H25" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="K25" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="26">
@@ -6977,35 +6977,35 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.8</v>
+        <v>22.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I26" t="n">
         <v>1.6</v>
       </c>
       <c r="J26" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="27">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.9</v>
+        <v>25.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G27" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="H27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="K27" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.8</v>
+        <v>22</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="G28" t="n">
-        <v>16.1</v>
+        <v>13.8</v>
       </c>
       <c r="H28" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K28" t="n">
         <v>2.4</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -7106,35 +7106,35 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>60.3</t>
+          <t>60.9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1.4</v>
       </c>
       <c r="G29" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="H29" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I29" t="n">
         <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="K29" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -7149,35 +7149,35 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>61.8</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="H30" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="I30" t="n">
         <v>1.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="K30" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="31">
@@ -7188,39 +7188,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>22.8</v>
+        <v>25.2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="G31" t="n">
-        <v>14.2</v>
+        <v>16.2</v>
       </c>
       <c r="H31" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="K31" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -497,39 +497,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G2" t="n">
         <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3">
@@ -540,39 +540,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>22.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -583,39 +583,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.4</v>
+        <v>21.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="5">
@@ -630,26 +630,26 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>2.7</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
@@ -720,22 +720,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I7" t="n">
         <v>1.5</v>
@@ -744,7 +744,7 @@
         <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -755,39 +755,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.6</v>
+        <v>22.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
         <v>6.3</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9">
@@ -798,39 +798,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="10">
@@ -845,26 +845,26 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="H10" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>1.9</v>
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25.4</v>
+        <v>23.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="H11" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
@@ -927,33 +927,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26.8</v>
+        <v>24.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="H12" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
         <v>0.4</v>
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.5</v>
+        <v>26.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="H13" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="14">
@@ -1013,27 +1013,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.6</v>
+        <v>25.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H14" t="n">
         <v>8.699999999999999</v>
@@ -1045,7 +1045,7 @@
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.1</v>
+        <v>23.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H15" t="n">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.8</v>
+        <v>23</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>24.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H17" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="18">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>24.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="H20" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="21">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="H21" t="n">
-        <v>7.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="22">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="H22" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="23">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1413,17 +1413,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G23" t="n">
         <v>6.2</v>
       </c>
       <c r="H23" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>2.2</v>
@@ -1451,22 +1451,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G24" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H24" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I24" t="n">
         <v>2.1</v>
@@ -1490,23 +1490,23 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H25" t="n">
         <v>7.8</v>
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K26" t="n">
         <v>3</v>
-      </c>
-      <c r="G26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.2</v>
       </c>
     </row>
     <row r="27">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26</v>
+        <v>25.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H28" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="29">
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.5</v>
+        <v>26.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="H29" t="n">
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K29" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1866,19 +1866,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>3.1</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H2" t="n">
         <v>5.2</v>
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.8</v>
+        <v>22.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H4" t="n">
         <v>5.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>22.8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.3</v>
+        <v>22.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -2077,16 +2077,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
         <v>1.6</v>
@@ -2148,7 +2148,7 @@
         <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -2159,11 +2159,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.9</v>
+        <v>22.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2172,26 +2172,26 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.9</v>
+        <v>23.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G11" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I12" t="n">
         <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -2331,30 +2331,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.9</v>
+        <v>23</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H13" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="I13" t="n">
         <v>1.8</v>
@@ -2363,7 +2363,7 @@
         <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="14">
@@ -2374,36 +2374,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.1</v>
+        <v>23.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
         <v>3.2</v>
@@ -2421,16 +2421,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,14 +2473,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>3.4</v>
       </c>
       <c r="G16" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="H16" t="n">
         <v>5.2</v>
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.8</v>
+        <v>23.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G17" t="n">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2554,31 +2554,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G18" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H18" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.5</v>
+        <v>23.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H19" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.2</v>
+        <v>22.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.8</v>
+        <v>24.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3.5</v>
       </c>
       <c r="G22" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="H25" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="26">
@@ -2890,33 +2890,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3.6</v>
       </c>
       <c r="G26" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H26" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0.6</v>
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G27" t="n">
         <v>6.8</v>
       </c>
       <c r="H27" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28">
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>7.8</v>
@@ -3048,7 +3048,7 @@
         <v>2.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K29" t="n">
         <v>2.3</v>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -3219,11 +3219,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3232,26 +3232,26 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="3">
@@ -3262,39 +3262,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K3" t="n">
         <v>3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="4">
@@ -3309,23 +3309,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H4" t="n">
         <v>3.8</v>
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3377,7 +3377,7 @@
         <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
         <v>2.5</v>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.5</v>
+        <v>22.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="G7" t="n">
         <v>7.6</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -3477,36 +3477,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>20.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>2.8</v>
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.6</v>
+        <v>21.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3595,7 +3595,7 @@
         <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -3649,30 +3649,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G12" t="n">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
         <v>1.7</v>
@@ -3681,7 +3681,7 @@
         <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>8.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.7</v>
+        <v>21.9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
         <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
@@ -3778,11 +3778,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.8</v>
+        <v>22.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3791,26 +3791,26 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="n">
         <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="16">
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.7</v>
+        <v>23.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="H18" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.8</v>
+        <v>22.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4006,14 +4006,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="H20" t="n">
         <v>4.4</v>
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4059,7 +4059,7 @@
         <v>8.9</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I21" t="n">
         <v>1.6</v>
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="H22" t="n">
         <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -4122,36 +4122,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.2</v>
+        <v>22.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G23" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="H23" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K23" t="n">
         <v>2.7</v>
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.4</v>
+        <v>23.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="25">
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4221,23 +4221,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="H25" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I25" t="n">
         <v>1.8</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K25" t="n">
         <v>2.6</v>
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.1</v>
+        <v>26.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="H26" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.4</v>
+        <v>24.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G27" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="H27" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K27" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="28">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4357,7 +4357,7 @@
         <v>2.9</v>
       </c>
       <c r="G28" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="H28" t="n">
         <v>4.5</v>
@@ -4366,7 +4366,7 @@
         <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K28" t="n">
         <v>1.9</v>
@@ -4393,17 +4393,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I29" t="n">
         <v>1.8</v>
@@ -4470,16 +4470,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4492,7 +4492,7 @@
         <v>4.7</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0.9</v>
@@ -4584,23 +4584,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -4623,39 +4623,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>10.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
         <v>1.5</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="4">
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.6</v>
+        <v>20.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="5">
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
-        <v>8.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4752,20 +4752,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.7</v>
+        <v>21.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4775,16 +4775,16 @@
         <v>10.8</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I6" t="n">
         <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.1</v>
+        <v>22.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>9.300000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J7" t="n">
         <v>1.6</v>
       </c>
-      <c r="J7" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K7" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.1</v>
+        <v>21.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
         <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.6</v>
+        <v>23</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
         <v>2.1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.2</v>
+        <v>22.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K11" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G11" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.1</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.6</v>
+        <v>23.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="G12" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>21.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="G13" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -5104,25 +5104,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="H14" t="n">
         <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.4</v>
+        <v>22.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G15" t="n">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
         <v>1.2</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="16">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>1.2</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="17">
@@ -5268,36 +5268,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="G18" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K18" t="n">
         <v>2.7</v>
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="H20" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="G21" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>1.2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
@@ -5444,20 +5444,20 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
         <v>11.3</v>
@@ -5487,23 +5487,23 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>2.3</v>
       </c>
       <c r="G23" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="H23" t="n">
         <v>3.4</v>
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.7</v>
+        <v>22.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J26" t="n">
         <v>1.6</v>
       </c>
-      <c r="J26" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K26" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -5741,39 +5741,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.3</v>
+        <v>24.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K29" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G29" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.6</v>
+        <v>27.4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="G30" t="n">
-        <v>12.4</v>
+        <v>10.9</v>
       </c>
       <c r="H30" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K30" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -5988,16 +5988,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.7</v>
+        <v>20.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G4" t="n">
-        <v>14.8</v>
+        <v>14.1</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.1</v>
+        <v>19.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.2</v>
+        <v>21.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.6</v>
+        <v>21.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1.4</v>
       </c>
       <c r="G7" t="n">
-        <v>14.2</v>
+        <v>14.9</v>
       </c>
       <c r="H7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -6199,33 +6199,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.8</v>
+        <v>19.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="G8" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -6242,36 +6242,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.7</v>
+        <v>18.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I9" t="n">
         <v>1.1</v>
       </c>
-      <c r="G9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>2.6</v>
@@ -6289,11 +6289,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -6311,7 +6311,7 @@
         <v>3.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>1.3</v>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I11" t="n">
         <v>1.2</v>
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20.6</v>
+        <v>21.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>12.2</v>
+        <v>13.6</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.6</v>
+        <v>20.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I13" t="n">
         <v>1.4</v>
-      </c>
-      <c r="G13" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.7</v>
       </c>
       <c r="J13" t="n">
         <v>1.9</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20.6</v>
+        <v>21.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G14" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="15">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6520,7 +6520,7 @@
         <v>0.7</v>
       </c>
       <c r="G15" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="H15" t="n">
         <v>3.7</v>
@@ -6529,7 +6529,7 @@
         <v>1.6</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
         <v>2.8</v>
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.7</v>
+        <v>19.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="G16" t="n">
-        <v>13.5</v>
+        <v>14.6</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
         <v>1.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="17">
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>19.3</v>
+        <v>21.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="G18" t="n">
-        <v>14.7</v>
+        <v>15.5</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>15.8</v>
+        <v>11.6</v>
       </c>
       <c r="H19" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="20">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.1</v>
+        <v>21.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="G20" t="n">
-        <v>11.6</v>
+        <v>15.7</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>15.7</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.4</v>
+        <v>22.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="H22" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K22" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.9</v>
+        <v>21.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="H23" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
         <v>2.3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.2</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21.4</v>
+        <v>23.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>14.2</v>
+        <v>15.6</v>
       </c>
       <c r="H24" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K24" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -6934,11 +6934,11 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -6973,39 +6973,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.8</v>
+        <v>21.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G26" t="n">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="K26" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="27">
@@ -7024,22 +7024,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
         <v>14.4</v>
       </c>
       <c r="H27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I27" t="n">
         <v>1.6</v>
@@ -7106,35 +7106,35 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
         <v>1.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K29" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="30">
@@ -7149,23 +7149,23 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25.2</v>
+        <v>24.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1.4</v>
       </c>
       <c r="G30" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="H30" t="n">
         <v>4.4</v>
@@ -7174,10 +7174,10 @@
         <v>1.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K30" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="31">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -497,39 +497,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H2" t="n">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -540,39 +540,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
         <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="4">
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="H5" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H6" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.6</v>
       </c>
     </row>
     <row r="7">
@@ -755,39 +755,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H8" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="9">
@@ -798,39 +798,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.3</v>
+        <v>22.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="10">
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.2</v>
+        <v>26.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G11" t="n">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="H11" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
         <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="12">
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.6</v>
+        <v>25.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>1.9</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="13">
@@ -970,33 +970,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26.6</v>
+        <v>24.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="H13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
         <v>0.4</v>
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25.8</v>
+        <v>24.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="15">
@@ -1099,36 +1099,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="H16" t="n">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K16" t="n">
         <v>2.8</v>
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.5</v>
+        <v>23</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0.6</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1257,7 +1257,7 @@
         <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.4</v>
+        <v>23.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="21">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="H21" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="22">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.4</v>
+        <v>25.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K23" t="n">
         <v>3.4</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -1443,33 +1443,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.8</v>
+        <v>24.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="G24" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H24" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
@@ -1486,39 +1486,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="H25" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>25.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="H26" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="27">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1615,33 +1615,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25.2</v>
+        <v>24.5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="H28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0.6</v>
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.3</v>
+        <v>24.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G29" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="30">
@@ -1701,39 +1701,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.6</v>
+        <v>26.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G30" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="H30" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I30" t="n">
         <v>2.1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K30" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1748,20 +1748,20 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G31" t="n">
         <v>6.4</v>
@@ -1905,23 +1905,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H3" t="n">
         <v>4.9</v>
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="G5" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I5" t="n">
         <v>1.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I6" t="n">
         <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2225,7 +2225,7 @@
         <v>6.3</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I10" t="n">
         <v>1.5</v>
@@ -2292,11 +2292,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>3.5</v>
       </c>
       <c r="G18" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H18" t="n">
         <v>5.5</v>
@@ -2578,7 +2578,7 @@
         <v>0.7</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.8</v>
+        <v>22.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G19" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H19" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="20">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.2</v>
+        <v>23.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G21" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H21" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2996,7 +2996,7 @@
         <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="H28" t="n">
         <v>6</v>
@@ -3062,39 +3062,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.2</v>
+        <v>24.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="G30" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="H30" t="n">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K30" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="31">
@@ -3105,39 +3105,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.7</v>
+        <v>26.1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G31" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="H31" t="n">
-        <v>5.3</v>
+        <v>6.7</v>
       </c>
       <c r="I31" t="n">
         <v>1.9</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -3262,39 +3262,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4">
@@ -3305,39 +3305,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -3348,39 +3348,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.3</v>
+        <v>22.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.5</v>
+        <v>21.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
         <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.7</v>
+        <v>20.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>8.300000000000001</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.8</v>
+        <v>21.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.9</v>
+        <v>22.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="G14" t="n">
-        <v>6.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
         <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.6</v>
+        <v>21.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G15" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
         <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.4</v>
+        <v>22.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="H16" t="n">
         <v>4.7</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="17">
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -3887,10 +3887,10 @@
         <v>6.9</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0.6</v>
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.8</v>
+        <v>22.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G18" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.7</v>
+        <v>23.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -4079,36 +4079,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.2</v>
+        <v>22.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K22" t="n">
         <v>2.7</v>
@@ -4122,36 +4122,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.1</v>
+        <v>23.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H23" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="I23" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K23" t="n">
         <v>2.7</v>
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H24" t="n">
         <v>5.4</v>
@@ -4194,7 +4194,7 @@
         <v>1.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K24" t="n">
         <v>2.1</v>
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>26.1</v>
+        <v>24.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G26" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.1</v>
+        <v>26.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="H27" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28">
@@ -4427,16 +4427,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -4446,16 +4446,16 @@
         <v>7.8</v>
       </c>
       <c r="H30" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -4627,16 +4627,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.1</v>
+        <v>22.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>9.300000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J4" t="n">
         <v>1.6</v>
       </c>
-      <c r="J4" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K4" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>3.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
         <v>1.2</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="7">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I7" t="n">
         <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.4</v>
+        <v>22.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4904,13 +4904,13 @@
         <v>9.5</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
         <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
         <v>2.7</v>
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>21.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.1</v>
+        <v>23</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="12">
@@ -5268,36 +5268,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.6</v>
+        <v>22.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G18" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K18" t="n">
         <v>2.7</v>
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.7</v>
+        <v>23.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -5354,36 +5354,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G20" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="H20" t="n">
         <v>3.4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="K20" t="n">
         <v>2.7</v>
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.7</v>
+        <v>22.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>10.2</v>
+        <v>11.3</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.5</v>
+        <v>21.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>11.3</v>
+        <v>10.2</v>
       </c>
       <c r="H22" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -5483,36 +5483,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G23" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="H23" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K23" t="n">
         <v>2.7</v>
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.6</v>
+        <v>22.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J25" t="n">
         <v>1.6</v>
       </c>
-      <c r="J25" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22.8</v>
+        <v>24.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G26" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="H26" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="K26" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="27">
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.1</v>
+        <v>23.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G27" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H27" t="n">
         <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>1.1</v>
       </c>
       <c r="K27" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="28">
@@ -5702,7 +5702,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5711,11 +5711,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G28" t="n">
         <v>10.6</v>
@@ -5831,23 +5831,23 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="H31" t="n">
         <v>5.3</v>
@@ -5859,7 +5859,7 @@
         <v>1.6</v>
       </c>
       <c r="K31" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>
@@ -5949,7 +5949,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5961,7 +5961,7 @@
         <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="H2" t="n">
         <v>3.3</v>
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
-        <v>14.1</v>
+        <v>14.8</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19.2</v>
+        <v>21.8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>14.5</v>
+        <v>14.9</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.1</v>
+        <v>20.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I6" t="n">
         <v>1.2</v>
       </c>
-      <c r="G6" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J6" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.8</v>
+        <v>19.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1.4</v>
       </c>
       <c r="G7" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -6379,31 +6379,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G12" t="n">
-        <v>13.6</v>
+        <v>14.8</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="13">
@@ -6418,11 +6418,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6437,16 +6437,16 @@
         <v>12.2</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>1.9</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -6465,31 +6465,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I14" t="n">
         <v>1.3</v>
       </c>
-      <c r="G14" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.7</v>
-      </c>
       <c r="J14" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>14.3</v>
+        <v>15.5</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
         <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.1</v>
+        <v>22.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="G18" t="n">
-        <v>15.5</v>
+        <v>11.6</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.1</v>
+        <v>21.4</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="G19" t="n">
-        <v>11.6</v>
+        <v>14.4</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
         <v>15.7</v>
       </c>
       <c r="H20" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G21" t="n">
         <v>15.7</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22">
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -6824,7 +6824,7 @@
         <v>14.4</v>
       </c>
       <c r="H22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
         <v>1.4</v>
@@ -6833,7 +6833,7 @@
         <v>2.3</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.7</v>
+        <v>21.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G24" t="n">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -6973,39 +6973,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>21.5</v>
+        <v>23.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>14.3</v>
+        <v>15.6</v>
       </c>
       <c r="H26" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K26" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -497,39 +497,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
@@ -540,39 +540,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H3" t="n">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -587,26 +587,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G4" t="n">
         <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I4" t="n">
         <v>1.8</v>
@@ -669,30 +669,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H6" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -701,7 +701,7 @@
         <v>0.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -768,17 +768,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I8" t="n">
         <v>1.8</v>
@@ -798,39 +798,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="H9" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -864,7 +864,7 @@
         <v>6.3</v>
       </c>
       <c r="H10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I10" t="n">
         <v>1.9</v>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -907,7 +907,7 @@
         <v>6.1</v>
       </c>
       <c r="H11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I11" t="n">
         <v>1.8</v>
@@ -916,7 +916,7 @@
         <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="12">
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.8</v>
+        <v>22.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K12" t="n">
         <v>2.8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.6</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24.6</v>
+        <v>23.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.6</v>
+        <v>23.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="H14" t="n">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="15">
@@ -1056,36 +1056,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.9</v>
+        <v>25.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H15" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
         <v>3.6</v>
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.2</v>
+        <v>24.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="H16" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0.4</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="H17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="H18" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
         <v>0.6</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H19" t="n">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I19" t="n">
         <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="H20" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="21">
@@ -1322,25 +1322,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H21" t="n">
         <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0.5</v>
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25.9</v>
+        <v>24.4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G23" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="H23" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -1443,33 +1443,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.4</v>
+        <v>25.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="G24" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="H24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
@@ -1486,39 +1486,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.8</v>
+        <v>26</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="H25" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K25" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="26">
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.2</v>
+        <v>25</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1558,7 +1558,7 @@
         <v>2.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
         <v>3.1</v>
@@ -1572,15 +1572,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1589,22 +1589,22 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>6</v>
-      </c>
-      <c r="H27" t="n">
-        <v>8</v>
-      </c>
-      <c r="I27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="H28" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="29">
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.5</v>
+        <v>26</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="H29" t="n">
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K29" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="30">
@@ -1701,39 +1701,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.3</v>
+        <v>24.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G30" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="H30" t="n">
         <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="31">
@@ -1862,16 +1862,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1881,7 +1881,7 @@
         <v>6.5</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -1890,7 +1890,7 @@
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3">
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="G4" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H5" t="n">
         <v>5.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G8" t="n">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>23.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -2245,30 +2245,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.6</v>
+        <v>23.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
         <v>1.6</v>
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H12" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I13" t="n">
         <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>3.5</v>
       </c>
       <c r="G15" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2468,19 +2468,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G16" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="H16" t="n">
         <v>5.2</v>
@@ -2492,7 +2492,7 @@
         <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.6</v>
+        <v>22.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="n">
         <v>6.6</v>
       </c>
       <c r="H17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.2</v>
+        <v>23.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K19" t="n">
         <v>2.9</v>
-      </c>
-      <c r="G19" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="H19" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.1</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G20" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -2679,16 +2679,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -2704,10 +2704,10 @@
         <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G22" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -2769,19 +2769,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>3.9</v>
       </c>
       <c r="G23" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H23" t="n">
         <v>5.5</v>
@@ -2793,7 +2793,7 @@
         <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2817,20 +2817,20 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>3.1</v>
       </c>
       <c r="G24" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H24" t="n">
         <v>5.3</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0.7</v>
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.1</v>
+        <v>23.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G25" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="G26" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="H26" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3066,11 +3066,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3091,10 +3091,10 @@
         <v>1.9</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="31">
@@ -3232,14 +3232,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
         <v>3.9</v>
@@ -3266,23 +3266,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>3.8</v>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3318,14 +3318,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="H4" t="n">
         <v>4</v>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3371,13 +3371,13 @@
         <v>8.6</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I5" t="n">
         <v>1.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K5" t="n">
         <v>3.1</v>
@@ -3438,11 +3438,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3454,19 +3454,19 @@
         <v>2.9</v>
       </c>
       <c r="G7" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
         <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.7</v>
+        <v>20.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.5</v>
+        <v>21.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.2</v>
+        <v>22.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
         <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.7</v>
+        <v>21.2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -3692,11 +3692,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3705,26 +3705,26 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="H13" t="n">
         <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H14" t="n">
         <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.9</v>
+        <v>22.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="G15" t="n">
-        <v>6.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
         <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.6</v>
+        <v>22.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="H16" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
         <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="H18" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
         <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.8</v>
+        <v>22.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.8</v>
+        <v>23.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="H20" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4065,7 +4065,7 @@
         <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K21" t="n">
         <v>2.5</v>
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.1</v>
+        <v>23.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="23">
@@ -4122,36 +4122,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.2</v>
+        <v>22.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G23" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="H23" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K23" t="n">
         <v>2.7</v>
@@ -4208,36 +4208,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.6</v>
+        <v>26.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="G25" t="n">
-        <v>8.9</v>
+        <v>7.2</v>
       </c>
       <c r="H25" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
         <v>1.8</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
         <v>2.6</v>
@@ -4255,23 +4255,23 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G26" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="H26" t="n">
         <v>4.7</v>
@@ -4283,7 +4283,7 @@
         <v>0.9</v>
       </c>
       <c r="K26" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.1</v>
+        <v>23.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K27" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="28">
@@ -4337,30 +4337,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I28" t="n">
         <v>1.9</v>
@@ -4369,7 +4369,7 @@
         <v>0.9</v>
       </c>
       <c r="K28" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="29">
@@ -4384,26 +4384,26 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G29" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
         <v>1.8</v>
@@ -4470,29 +4470,29 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3.3</v>
       </c>
       <c r="G31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="H31" t="n">
         <v>4.7</v>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0.9</v>
@@ -4584,16 +4584,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4609,10 +4609,10 @@
         <v>1.3</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -4623,39 +4623,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.1</v>
+        <v>21.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="G3" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>1.5</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.8</v>
+        <v>21.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="G4" t="n">
-        <v>10.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5">
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.9</v>
+        <v>21.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="6">
@@ -4752,11 +4752,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.1</v>
+        <v>20.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4765,26 +4765,26 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>9.300000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H7" t="n">
         <v>3.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
         <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.1</v>
+        <v>22.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>10.7</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -4881,36 +4881,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G9" t="n">
-        <v>9.5</v>
+        <v>10.1</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K9" t="n">
         <v>2.7</v>
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.4</v>
+        <v>22.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>1.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K11" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.1</v>
       </c>
     </row>
     <row r="12">
@@ -5014,16 +5014,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -5042,7 +5042,7 @@
         <v>1.3</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -5104,12 +5104,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -5119,7 +5119,7 @@
         <v>10.7</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
         <v>1.5</v>
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.5</v>
+        <v>23.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G17" t="n">
-        <v>9.300000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.7</v>
+        <v>22.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>10.2</v>
+        <v>11.3</v>
       </c>
       <c r="H19" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.7</v>
+        <v>21.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="H20" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="I20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J20" t="n">
         <v>1.6</v>
       </c>
-      <c r="J20" t="n">
-        <v>0.9</v>
-      </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.5</v>
+        <v>23.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G21" t="n">
-        <v>11.3</v>
+        <v>10.1</v>
       </c>
       <c r="H21" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.8</v>
+        <v>23.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="G22" t="n">
         <v>10.2</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.6</v>
+        <v>22.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
-        <v>10.3</v>
+        <v>9.4</v>
       </c>
       <c r="H23" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="24">
@@ -5530,26 +5530,26 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G24" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="H24" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I24" t="n">
         <v>1.7</v>
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.8</v>
+        <v>23.5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G25" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="K25" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -5663,31 +5663,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K27" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28">
@@ -5698,39 +5698,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="G28" t="n">
-        <v>10.6</v>
+        <v>9.6</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I28" t="n">
         <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="29">
@@ -5745,32 +5745,32 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G29" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="H29" t="n">
         <v>4.6</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
         <v>2.6</v>
@@ -5788,16 +5788,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27.4</v>
+        <v>27.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -5810,7 +5810,7 @@
         <v>4.4</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>1.3</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -6013,7 +6013,7 @@
         <v>1.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="K3" t="n">
         <v>2.8</v>
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>20.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I4" t="n">
         <v>1.2</v>
       </c>
-      <c r="G4" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J4" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.8</v>
+        <v>21</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
         <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.5</v>
+        <v>21.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>14.1</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="7">
@@ -6203,23 +6203,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1.1</v>
       </c>
       <c r="G8" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -6246,16 +6246,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -6289,23 +6289,23 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="H10" t="n">
         <v>3.9</v>
@@ -6328,11 +6328,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.3</v>
+        <v>18.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6341,26 +6341,26 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.5</v>
       </c>
-      <c r="G11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.6</v>
+        <v>22.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>14.8</v>
+        <v>13.5</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G13" t="n">
-        <v>12.2</v>
+        <v>15</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="14">
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -6470,17 +6470,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1.4</v>
       </c>
       <c r="G14" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
         <v>1.3</v>
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18.3</v>
+        <v>19.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>0.7</v>
       </c>
       <c r="G15" t="n">
-        <v>13.8</v>
+        <v>14.7</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19.2</v>
+        <v>20.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
-        <v>14.6</v>
+        <v>12.2</v>
       </c>
       <c r="H16" t="n">
         <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.1</v>
+        <v>22</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>15.5</v>
+        <v>11.6</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.1</v>
+        <v>21.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="G18" t="n">
-        <v>11.6</v>
+        <v>14.4</v>
       </c>
       <c r="H18" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -6672,15 +6672,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6692,16 +6692,16 @@
         <v>1.2</v>
       </c>
       <c r="G19" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I19" t="n">
         <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K19" t="n">
         <v>2.4</v>
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G20" t="n">
         <v>15.7</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
         <v>15.7</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21.5</v>
+        <v>24.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="G24" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="H24" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I24" t="n">
         <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.8</v>
+        <v>21.5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="G25" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="I25" t="n">
         <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="K25" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26">
@@ -6977,35 +6977,35 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.7</v>
+        <v>24</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>1.5</v>
       </c>
       <c r="K26" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="27">
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="H27" t="n">
         <v>4.6</v>
@@ -7045,7 +7045,7 @@
         <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="K27" t="n">
         <v>2.3</v>
@@ -7063,11 +7063,11 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -7091,7 +7091,7 @@
         <v>2.4</v>
       </c>
       <c r="K28" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="29">
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -7115,26 +7115,26 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="H29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I29" t="n">
         <v>1.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="30">
@@ -7149,11 +7149,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -7165,19 +7165,19 @@
         <v>1.4</v>
       </c>
       <c r="G30" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="H30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I30" t="n">
         <v>1.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -553,26 +553,26 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H3" t="n">
         <v>7.4</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="4">
@@ -587,26 +587,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
         <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I4" t="n">
         <v>1.8</v>
@@ -615,7 +615,7 @@
         <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="5">
@@ -634,12 +634,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -669,30 +669,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -701,7 +701,7 @@
         <v>0.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -712,30 +712,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H7" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -744,7 +744,7 @@
         <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="8">
@@ -802,11 +802,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -818,7 +818,7 @@
         <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H9" t="n">
         <v>8.9</v>
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26.5</v>
+        <v>22.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="H11" t="n">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J11" t="n">
         <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.9</v>
+        <v>26.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G12" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="H12" t="n">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>0.4</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="H13" t="n">
-        <v>8.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="15">
@@ -1099,36 +1099,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="H16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
         <v>3.4</v>
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="H17" t="n">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.5</v>
+        <v>24.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G18" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H18" t="n">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="H19" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="20">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.4</v>
+        <v>23.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="22">
@@ -1357,30 +1357,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.1</v>
+        <v>23.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="H22" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="I22" t="n">
         <v>1.9</v>
@@ -1389,7 +1389,7 @@
         <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -1494,12 +1494,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="H27" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="28">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1623,31 +1623,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
       <c r="H28" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="29">
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1681,7 +1681,7 @@
         <v>6.5</v>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="I29" t="n">
         <v>2.1</v>
@@ -1701,39 +1701,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G30" t="n">
-        <v>7.1</v>
+        <v>5.6</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K30" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="31">
@@ -1862,16 +1862,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1881,7 +1881,7 @@
         <v>6.5</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1991,23 +1991,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H5" t="n">
         <v>5.2</v>
@@ -2016,7 +2016,7 @@
         <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K5" t="n">
         <v>2.4</v>
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2142,13 +2142,13 @@
         <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
         <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -2163,23 +2163,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H9" t="n">
         <v>4.9</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2210,31 +2210,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G11" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="H12" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="H13" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H14" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -2546,36 +2546,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G18" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="H18" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="n">
         <v>2.9</v>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2597,28 +2597,28 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H19" t="n">
         <v>5.7</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K19" t="n">
         <v>2.9</v>
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>3.6</v>
       </c>
       <c r="G25" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="H25" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.1</v>
+        <v>23.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="G26" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H26" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="G27" t="n">
         <v>6.8</v>
       </c>
       <c r="H27" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="28">
@@ -2984,19 +2984,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="H28" t="n">
         <v>6</v>
@@ -3266,16 +3266,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3361,11 +3361,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>8.6</v>
@@ -3395,11 +3395,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3481,20 +3481,20 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="n">
         <v>7.8</v>
@@ -3509,7 +3509,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -3567,16 +3567,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.3</v>
+        <v>21.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.2</v>
+        <v>22.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.3</v>
+        <v>22.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.5</v>
+        <v>21.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
         <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
@@ -3786,19 +3786,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>3.2</v>
       </c>
       <c r="G15" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H15" t="n">
         <v>4.8</v>
@@ -3872,25 +3872,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="H17" t="n">
         <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
         <v>0.6</v>
@@ -3915,19 +3915,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>2.9</v>
       </c>
       <c r="G18" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="H18" t="n">
         <v>4.4</v>
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.7</v>
+        <v>23.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.8</v>
+        <v>22.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -4427,16 +4427,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4603,7 +4603,7 @@
         <v>10.1</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -4627,16 +4627,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -4652,7 +4652,7 @@
         <v>1.5</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -4670,23 +4670,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1.9</v>
       </c>
       <c r="G4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="H4" t="n">
         <v>3.5</v>
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.3</v>
+        <v>22.8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
         <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.9</v>
+        <v>21.3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.1</v>
+        <v>22.6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.8</v>
+        <v>20.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G8" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J8" t="n">
         <v>1.3</v>
       </c>
-      <c r="J8" t="n">
-        <v>1.6</v>
-      </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.1</v>
+        <v>20.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>10.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
         <v>1.2</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.7</v>
+        <v>22.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
         <v>9.5</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11">
@@ -4967,36 +4967,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G11" t="n">
-        <v>9.5</v>
+        <v>10.1</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K11" t="n">
         <v>2.7</v>
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K13" t="n">
         <v>2.4</v>
-      </c>
-      <c r="G13" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G15" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="16">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>2.4</v>
       </c>
       <c r="G16" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="I16" t="n">
         <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>1.2</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="H18" t="n">
         <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G19" t="n">
-        <v>11.3</v>
+        <v>10.1</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.8</v>
+        <v>23.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="G20" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.8</v>
+        <v>22.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0.9</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G23" t="n">
-        <v>9.4</v>
+        <v>11.6</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I23" t="n">
         <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.3</v>
+        <v>22.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="G24" t="n">
-        <v>11.6</v>
+        <v>10.2</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.5</v>
+        <v>24.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="H25" t="n">
         <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>1.1</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.2</v>
+        <v>23.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="G26" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H26" t="n">
         <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>1.1</v>
       </c>
       <c r="K26" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="27">
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="G27" t="n">
-        <v>10.6</v>
+        <v>9.6</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I27" t="n">
         <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="28">
@@ -5698,39 +5698,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G28" t="n">
-        <v>9.6</v>
+        <v>10.7</v>
       </c>
       <c r="H28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I28" t="n">
         <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K28" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="29">
@@ -5964,7 +5964,7 @@
         <v>13.3</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
         <v>1.7</v>
@@ -5988,35 +5988,35 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.2</v>
+        <v>19.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J3" t="n">
         <v>1.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>19.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>14.8</v>
+        <v>14.1</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.2</v>
+        <v>21.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -6242,33 +6242,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.1</v>
+        <v>19.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -6289,16 +6289,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -6308,7 +6308,7 @@
         <v>13.3</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
         <v>1.5</v>
@@ -6317,7 +6317,7 @@
         <v>1.3</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="11">
@@ -6375,26 +6375,26 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I12" t="n">
         <v>1.2</v>
@@ -6418,35 +6418,35 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G13" t="n">
         <v>15</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
         <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.5</v>
+        <v>19.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="G14" t="n">
-        <v>13.7</v>
+        <v>14.7</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
         <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="G15" t="n">
-        <v>14.7</v>
+        <v>12.3</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.7</v>
+        <v>21.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G16" t="n">
-        <v>12.2</v>
+        <v>13.7</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J16" t="n">
         <v>1.5</v>
       </c>
-      <c r="J16" t="n">
-        <v>1.9</v>
-      </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
@@ -6629,15 +6629,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>1.2</v>
       </c>
       <c r="G18" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
         <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K18" t="n">
         <v>2.4</v>
@@ -6672,30 +6672,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
       </c>
       <c r="G19" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I19" t="n">
         <v>1.3</v>
@@ -6704,7 +6704,7 @@
         <v>1.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1.2</v>
       </c>
       <c r="G20" t="n">
-        <v>15.7</v>
+        <v>14.4</v>
       </c>
       <c r="H20" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
         <v>1.3</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.5</v>
+        <v>24.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G23" t="n">
-        <v>14.1</v>
+        <v>14.6</v>
       </c>
       <c r="H23" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.6</v>
+        <v>21.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I24" t="n">
         <v>1.6</v>
       </c>
-      <c r="G24" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.7</v>
-      </c>
       <c r="J24" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="25">
@@ -7016,15 +7016,15 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="G27" t="n">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="H27" t="n">
         <v>4.6</v>
@@ -7045,10 +7045,10 @@
         <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="28">
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="G28" t="n">
-        <v>15.8</v>
+        <v>14.3</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="29">
@@ -7102,39 +7102,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>67.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G29" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="H29" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="K29" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -7192,32 +7192,32 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1.2</v>
       </c>
       <c r="G31" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="H31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I31" t="n">
         <v>1.9</v>
       </c>
       <c r="J31" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K31" t="n">
         <v>2.7</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -497,15 +497,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -514,22 +514,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
         <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="3">
@@ -540,15 +540,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -557,22 +557,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
@@ -634,12 +634,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="H6" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -755,11 +755,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.5</v>
+        <v>22.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -768,26 +768,26 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H8" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -798,39 +798,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.4</v>
+        <v>22.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="H9" t="n">
-        <v>8.9</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="10">
@@ -849,25 +849,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H10" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>0.6</v>
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.9</v>
+        <v>23.4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -935,12 +935,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -950,13 +950,13 @@
         <v>6.1</v>
       </c>
       <c r="H12" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
         <v>3.4</v>
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="H13" t="n">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
         <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -1017,11 +1017,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.6</v>
+        <v>23.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="H16" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="17">
@@ -1142,11 +1142,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.7</v>
+        <v>23.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G18" t="n">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="H18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="19">
@@ -1228,20 +1228,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1251,16 +1251,16 @@
         <v>6.1</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I19" t="n">
         <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.2</v>
+        <v>24.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="H20" t="n">
-        <v>9.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="21">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="H21" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="22">
@@ -1357,30 +1357,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G22" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="H22" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="I22" t="n">
         <v>1.9</v>
@@ -1389,7 +1389,7 @@
         <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="23">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="H24" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="25">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1494,31 +1494,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="H25" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -1529,36 +1529,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="H26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
         <v>3.1</v>
@@ -1585,17 +1585,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H27" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="I27" t="n">
         <v>2.6</v>
@@ -1604,7 +1604,7 @@
         <v>0.5</v>
       </c>
       <c r="K27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="H28" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.1</v>
+        <v>24.9</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G29" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K29" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="30">
@@ -1701,39 +1701,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.6</v>
+        <v>26.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G30" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="H30" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="I30" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K30" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="31">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1770,7 +1770,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J31" t="n">
         <v>0.6</v>
@@ -1905,23 +1905,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H3" t="n">
         <v>4.9</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1957,14 +1957,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>2.7</v>
       </c>
       <c r="G4" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H4" t="n">
         <v>5.1</v>
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -2077,16 +2077,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.2</v>
+        <v>22.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.9</v>
+        <v>23.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.4</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.1</v>
+        <v>23.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -2460,36 +2460,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="G16" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="I16" t="n">
         <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K16" t="n">
         <v>2.2</v>
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.1</v>
+        <v>23</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="G17" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="H17" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="I17" t="n">
         <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2569,7 +2569,7 @@
         <v>6.6</v>
       </c>
       <c r="H18" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I18" t="n">
         <v>1.4</v>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2597,31 +2597,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H19" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -2632,11 +2632,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.1</v>
+        <v>23.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2645,26 +2645,26 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I20" t="n">
         <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="21">
@@ -2675,11 +2675,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.6</v>
+        <v>24.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,26 +2688,26 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3.4</v>
       </c>
       <c r="G21" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H21" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -2726,22 +2726,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3.6</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="H22" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
         <v>1.5</v>
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>23.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="G23" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H23" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="24">
@@ -2808,11 +2808,11 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2824,13 +2824,13 @@
         <v>3.1</v>
       </c>
       <c r="G24" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H24" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0.7</v>
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.3</v>
+        <v>24.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="G25" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H25" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.9</v>
+        <v>23.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="G26" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="H26" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="27">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.1</v>
+        <v>23.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="G27" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H27" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28">
@@ -2984,22 +2984,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I28" t="n">
         <v>1.8</v>
@@ -3027,19 +3027,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H29" t="n">
         <v>5.6</v>
@@ -3051,7 +3051,7 @@
         <v>0.6</v>
       </c>
       <c r="K29" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="30">
@@ -3066,16 +3066,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -3085,7 +3085,7 @@
         <v>7.2</v>
       </c>
       <c r="H30" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I30" t="n">
         <v>1.9</v>
@@ -3113,16 +3113,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G31" t="n">
         <v>6.8</v>
@@ -3137,7 +3137,7 @@
         <v>0.8</v>
       </c>
       <c r="K31" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>
@@ -3309,20 +3309,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
         <v>7.9</v>
@@ -3334,7 +3334,7 @@
         <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K4" t="n">
         <v>2.5</v>
@@ -3348,39 +3348,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K5" t="n">
         <v>3</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.9</v>
+        <v>21.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3457,7 +3457,7 @@
         <v>7.7</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
         <v>1.6</v>
@@ -3524,11 +3524,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3540,7 +3540,7 @@
         <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H9" t="n">
         <v>3.5</v>
@@ -3567,29 +3567,29 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="H10" t="n">
         <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0.5</v>
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.3</v>
+        <v>22.4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.3</v>
+        <v>21.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="n">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3748,14 +3748,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H14" t="n">
         <v>4.6</v>
@@ -3821,20 +3821,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -3844,13 +3844,13 @@
         <v>6.8</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
         <v>2.3</v>
@@ -3864,36 +3864,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K17" t="n">
         <v>2.3</v>
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="19">
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.6</v>
+        <v>22.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G19" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="20">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4036,39 +4036,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="22">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.2</v>
+        <v>22.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H22" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K22" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.1</v>
+        <v>24.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="G23" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="H23" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I23" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0.9</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G24" t="n">
-        <v>7.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0.9</v>
       </c>
       <c r="K24" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="25">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26.1</v>
+        <v>23.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="G25" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="H26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0.9</v>
       </c>
       <c r="K26" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.3</v>
+        <v>26.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28">
@@ -4337,30 +4337,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G28" t="n">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
       <c r="H28" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
         <v>1.9</v>
@@ -4369,7 +4369,7 @@
         <v>0.9</v>
       </c>
       <c r="K28" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="29">
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>2.9</v>
       </c>
       <c r="G29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="H29" t="n">
         <v>4.5</v>
@@ -4470,26 +4470,26 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G31" t="n">
         <v>8.9</v>
       </c>
       <c r="H31" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4689,7 +4689,7 @@
         <v>8.9</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
         <v>1.5</v>
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.6</v>
+        <v>19.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -4851,17 +4851,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1.8</v>
       </c>
       <c r="G8" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I8" t="n">
         <v>1.5</v>
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.1</v>
+        <v>22.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
         <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4941,16 +4941,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="H10" t="n">
         <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G12" t="n">
         <v>10.6</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
         <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="G13" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
         <v>10.6</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="n">
         <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>2.4</v>
       </c>
       <c r="G15" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
         <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.3</v>
+        <v>23.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G18" t="n">
-        <v>11.3</v>
+        <v>10.1</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.8</v>
+        <v>22.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G20" t="n">
-        <v>10.3</v>
+        <v>11.6</v>
       </c>
       <c r="H20" t="n">
         <v>4.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>1.2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.7</v>
+        <v>23.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G21" t="n">
-        <v>9.4</v>
+        <v>10.3</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -5440,36 +5440,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.8</v>
+        <v>22.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="n">
-        <v>10.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="K22" t="n">
         <v>2.4</v>
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>2.4</v>
       </c>
       <c r="G23" t="n">
-        <v>11.6</v>
+        <v>10.3</v>
       </c>
       <c r="H23" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>1.2</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="24">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.2</v>
+        <v>23.5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>1.1</v>
       </c>
       <c r="K25" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.5</v>
+        <v>24.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G26" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="H26" t="n">
         <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>1.1</v>
       </c>
       <c r="K26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="27">
@@ -5659,16 +5659,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5678,16 +5678,16 @@
         <v>9.6</v>
       </c>
       <c r="H27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -5745,11 +5745,11 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G29" t="n">
         <v>12.4</v>
@@ -5770,7 +5770,7 @@
         <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K29" t="n">
         <v>2.6</v>
@@ -5792,19 +5792,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>2.6</v>
       </c>
       <c r="G30" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="H30" t="n">
         <v>4.4</v>
@@ -5816,7 +5816,7 @@
         <v>1.3</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="31">
@@ -5831,23 +5831,23 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26</v>
+        <v>26.3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="H31" t="n">
         <v>5.3</v>
@@ -5856,10 +5856,10 @@
         <v>1.7</v>
       </c>
       <c r="J31" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.4</v>
+        <v>21.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G4" t="n">
-        <v>14.1</v>
+        <v>14.8</v>
       </c>
       <c r="H4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19.1</v>
+        <v>21.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>14.1</v>
+        <v>14.9</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.9</v>
+        <v>19.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.1</v>
+        <v>20.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>14.8</v>
+        <v>14.2</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.4</v>
+        <v>22</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>14.4</v>
+        <v>13.4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
         <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>19.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="G10" t="n">
-        <v>13.3</v>
+        <v>14.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -6328,15 +6328,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -6345,22 +6345,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8</v>
+        <v>13.3</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I11" t="n">
         <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>18.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I12" t="n">
         <v>1.5</v>
       </c>
-      <c r="G12" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>15</v>
+        <v>13.6</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19.3</v>
+        <v>21.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G14" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>12.3</v>
+        <v>11.5</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.5</v>
+        <v>19.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="G16" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
         <v>1.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>20.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="G17" t="n">
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -6676,23 +6676,23 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
       </c>
       <c r="G19" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="H19" t="n">
         <v>3.9</v>
@@ -6719,23 +6719,23 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1.2</v>
       </c>
       <c r="G20" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="H20" t="n">
         <v>4.6</v>
@@ -6747,7 +6747,7 @@
         <v>1.9</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>15.7</v>
+        <v>14.1</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="22">
@@ -6801,27 +6801,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.8</v>
+        <v>21.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>14.4</v>
+        <v>15.7</v>
       </c>
       <c r="H22" t="n">
         <v>4</v>
@@ -6830,10 +6830,10 @@
         <v>1.4</v>
       </c>
       <c r="J22" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.6</v>
+        <v>22.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G23" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="H23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G24" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="H24" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="I24" t="n">
         <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K24" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21.5</v>
+        <v>24.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G25" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="H25" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I25" t="n">
         <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -6977,11 +6977,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -6996,7 +6996,7 @@
         <v>15.5</v>
       </c>
       <c r="H26" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
         <v>1.1</v>
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>67.7</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G27" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="H27" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K27" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="28">
@@ -7067,19 +7067,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>67.7</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1.6</v>
       </c>
       <c r="G28" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="H28" t="n">
         <v>4.6</v>
@@ -7102,39 +7102,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23.8</v>
+        <v>24.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G29" t="n">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="H29" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="K29" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="30">
@@ -7145,36 +7145,36 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.8</v>
+        <v>24.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>16</v>
+        <v>14.9</v>
       </c>
       <c r="H30" t="n">
         <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
         <v>2.6</v>
@@ -7192,16 +7192,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -7214,10 +7214,10 @@
         <v>4.3</v>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K31" t="n">
         <v>2.7</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -505,31 +505,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3">
@@ -540,39 +540,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.2</v>
+        <v>21.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
         <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -587,20 +587,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G4" t="n">
         <v>6.5</v>
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.4</v>
+        <v>23.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.2</v>
+        <v>21.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -759,23 +759,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="H8" t="n">
         <v>8.5</v>
@@ -849,12 +849,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -864,7 +864,7 @@
         <v>6.4</v>
       </c>
       <c r="H10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>26.5</v>
+        <v>23.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.9</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="13">
@@ -1013,36 +1013,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.4</v>
+        <v>25.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="H14" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
         <v>3.6</v>
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25.8</v>
+        <v>26.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="H15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G16" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="H17" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="18">
@@ -1193,19 +1193,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>3.4</v>
       </c>
       <c r="G18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
         <v>8.699999999999999</v>
@@ -1217,7 +1217,7 @@
         <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="19">
@@ -1275,11 +1275,11 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.8</v>
+        <v>24.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G22" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="H22" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
         <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="H23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="24">
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.9</v>
+        <v>26.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="H29" t="n">
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K29" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1701,39 +1701,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.1</v>
+        <v>24.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G30" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K30" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="31">
@@ -1862,11 +1862,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2081,31 +2081,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H7" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.7</v>
+        <v>23.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="G8" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2228,7 +2228,7 @@
         <v>4.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
         <v>0.8</v>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2296,31 +2296,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H12" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="14">
@@ -2374,30 +2374,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.3</v>
+        <v>22.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="H14" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I14" t="n">
         <v>1.8</v>
@@ -2406,7 +2406,7 @@
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G15" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16">
@@ -2460,30 +2460,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.1</v>
+        <v>23.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="G16" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="H16" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I16" t="n">
         <v>1.8</v>
@@ -2492,7 +2492,7 @@
         <v>0.7</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="17">
@@ -2546,24 +2546,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.6</v>
+        <v>22.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G18" t="n">
         <v>6.6</v>
@@ -2572,13 +2572,13 @@
         <v>5.8</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="19">
@@ -2589,11 +2589,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2602,26 +2602,26 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I19" t="n">
         <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2640,28 +2640,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H20" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
         <v>2.9</v>
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.1</v>
+        <v>23.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3.4</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2769,31 +2769,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="G23" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H23" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2812,31 +2812,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G24" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H24" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="G26" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H26" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="27">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="G27" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H27" t="n">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -3062,30 +3062,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.7</v>
+        <v>26.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="G30" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="H30" t="n">
-        <v>5.2</v>
+        <v>6.7</v>
       </c>
       <c r="I30" t="n">
         <v>1.9</v>
@@ -3094,7 +3094,7 @@
         <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31">
@@ -3105,30 +3105,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.1</v>
+        <v>24.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="H31" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="I31" t="n">
         <v>1.9</v>
@@ -3137,7 +3137,7 @@
         <v>0.8</v>
       </c>
       <c r="K31" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -3223,16 +3223,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3282,7 +3282,7 @@
         <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H3" t="n">
         <v>3.8</v>
@@ -3294,7 +3294,7 @@
         <v>0.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="4">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3380,7 +3380,7 @@
         <v>1.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.4</v>
+        <v>21.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
         <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.6</v>
+        <v>20.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.3</v>
+        <v>22.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H12" t="n">
         <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.3</v>
+        <v>21.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
@@ -3782,26 +3782,26 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>3.2</v>
       </c>
       <c r="G15" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I15" t="n">
         <v>1.7</v>
@@ -3810,7 +3810,7 @@
         <v>0.8</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3930,7 +3930,7 @@
         <v>7.7</v>
       </c>
       <c r="H18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I18" t="n">
         <v>1.5</v>
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -3976,7 +3976,7 @@
         <v>4.4</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
         <v>0.8</v>
@@ -4036,36 +4036,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G21" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H21" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K21" t="n">
         <v>2.1</v>
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.1</v>
+        <v>23.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="G23" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0.9</v>
       </c>
       <c r="K23" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="25">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.7</v>
+        <v>26.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>8.9</v>
+        <v>7.2</v>
       </c>
       <c r="H26" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.2</v>
+        <v>23.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K27" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="28">
@@ -4337,30 +4337,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I28" t="n">
         <v>1.9</v>
@@ -4369,7 +4369,7 @@
         <v>0.9</v>
       </c>
       <c r="K28" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="29">
@@ -4427,23 +4427,23 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H30" t="n">
         <v>4.8</v>
@@ -4455,7 +4455,7 @@
         <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31">
@@ -4584,16 +4584,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.9</v>
+        <v>20.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="H7" t="n">
         <v>3.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.9</v>
+        <v>19.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>10.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H8" t="n">
         <v>3.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
@@ -4889,28 +4889,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
         <v>0.9</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -4924,36 +4924,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K10" t="n">
         <v>2.7</v>
@@ -4967,36 +4967,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I11" t="n">
         <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>2.7</v>
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
         <v>10.6</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
         <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.5</v>
+        <v>22.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G13" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
         <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.6</v>
+        <v>22.3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G18" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.3</v>
+        <v>23.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G19" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -5491,19 +5491,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>2.4</v>
       </c>
       <c r="G23" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="H23" t="n">
         <v>3.9</v>
@@ -5534,19 +5534,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2.8</v>
       </c>
       <c r="G24" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="H24" t="n">
         <v>4.1</v>
@@ -5558,7 +5558,7 @@
         <v>1.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="25">
@@ -5741,39 +5741,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.5</v>
+        <v>27.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="G29" t="n">
-        <v>12.4</v>
+        <v>10.8</v>
       </c>
       <c r="H29" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K29" t="n">
         <v>1.9</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="30">
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27.3</v>
+        <v>24.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K30" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G30" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1.9</v>
       </c>
     </row>
     <row r="31">
@@ -5945,23 +5945,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="H2" t="n">
         <v>3.4</v>
@@ -5988,23 +5988,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="H3" t="n">
         <v>3.6</v>
@@ -6013,7 +6013,7 @@
         <v>1.1</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="K3" t="n">
         <v>2.7</v>
@@ -6031,26 +6031,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1.3</v>
       </c>
       <c r="G4" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="n">
         <v>1.3</v>
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.6</v>
+        <v>20.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.7</v>
+        <v>19.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
-        <v>14.2</v>
+        <v>14.7</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>19.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>13.4</v>
+        <v>14</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.1</v>
+        <v>18.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="G10" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11">
@@ -6332,11 +6332,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -6351,7 +6351,7 @@
         <v>13.3</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
         <v>1.5</v>
@@ -6360,7 +6360,7 @@
         <v>1.3</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="12">
@@ -6371,11 +6371,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18.4</v>
+        <v>21.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -6384,26 +6384,26 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="H12" t="n">
         <v>3.6</v>
       </c>
       <c r="I12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J12" t="n">
         <v>1.5</v>
       </c>
-      <c r="J12" t="n">
-        <v>1.4</v>
-      </c>
       <c r="K12" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -6461,20 +6461,20 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G14" t="n">
         <v>15</v>
@@ -6486,7 +6486,7 @@
         <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>3.1</v>
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.9</v>
+        <v>20.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="G15" t="n">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -6586,36 +6586,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K17" t="n">
         <v>2.4</v>
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>21.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>15.6</v>
+        <v>11.5</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>14.1</v>
+        <v>15.7</v>
       </c>
       <c r="H21" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.7</v>
+        <v>21.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G22" t="n">
-        <v>15.7</v>
+        <v>14.3</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="23">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21.2</v>
+        <v>24.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G24" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="H24" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.6</v>
+        <v>23.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J25" t="n">
         <v>1.5</v>
       </c>
-      <c r="G25" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>2.8</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -6973,39 +6973,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.9</v>
+        <v>21.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>15.5</v>
+        <v>14.2</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="27">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.9</v>
+        <v>23.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>15.8</v>
+        <v>14.5</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K27" t="n">
         <v>2.3</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="28">
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.2</v>
+        <v>23.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="G28" t="n">
-        <v>14.5</v>
+        <v>15.8</v>
       </c>
       <c r="H28" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="K28" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="29">
@@ -7102,39 +7102,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>16.1</v>
+        <v>14.9</v>
       </c>
       <c r="H29" t="n">
         <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="30">
@@ -7145,39 +7145,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G30" t="n">
-        <v>14.9</v>
+        <v>16.1</v>
       </c>
       <c r="H30" t="n">
         <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="31">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -497,15 +497,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -514,22 +514,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
         <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -540,15 +540,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -557,22 +557,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="4">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -649,7 +649,7 @@
         <v>5.6</v>
       </c>
       <c r="H5" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I5" t="n">
         <v>1.9</v>
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.2</v>
+        <v>21.3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.3</v>
+        <v>23.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -884,36 +884,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="H11" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="n">
         <v>2.9</v>
@@ -927,7 +927,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -935,31 +935,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K12" t="n">
         <v>2.9</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.6</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25.8</v>
+        <v>26.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="H14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.5</v>
+        <v>25.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="H15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.1</v>
+        <v>24.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="G16" t="n">
         <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H18" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="H19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.6</v>
+        <v>23.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="H20" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="21">
@@ -1318,23 +1318,23 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H21" t="n">
         <v>8</v>
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="H22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G23" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="H23" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1572,36 +1572,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="H27" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="I27" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K27" t="n">
         <v>3</v>
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="H28" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="29">
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.3</v>
+        <v>24.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G29" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="30">
@@ -1701,39 +1701,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.9</v>
+        <v>26.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="H30" t="n">
         <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K30" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1748,35 +1748,35 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3.7</v>
       </c>
       <c r="G31" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H31" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>2.3</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -1905,23 +1905,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H3" t="n">
         <v>4.9</v>
@@ -1933,7 +1933,7 @@
         <v>0.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.7</v>
+        <v>23.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H6" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I6" t="n">
         <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2081,31 +2081,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
         <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.3</v>
+        <v>22.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="H12" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.3</v>
+        <v>22.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="H13" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
         <v>6.5</v>
       </c>
       <c r="H14" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="16">
@@ -2460,20 +2460,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -2483,16 +2483,16 @@
         <v>6.3</v>
       </c>
       <c r="H16" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
         <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
@@ -2503,20 +2503,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2526,16 +2526,16 @@
         <v>6.3</v>
       </c>
       <c r="H17" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="I17" t="n">
         <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.1</v>
+        <v>23.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H18" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.9</v>
+        <v>22</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="20">
@@ -2675,11 +2675,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,26 +2688,26 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3.4</v>
       </c>
       <c r="G21" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
         <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,11 +2731,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G22" t="n">
         <v>7.1</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2769,31 +2769,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G23" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H23" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="24">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2812,31 +2812,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H24" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="25">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2879,7 +2879,7 @@
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -2933,36 +2933,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="H27" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K27" t="n">
         <v>2.8</v>
@@ -2976,36 +2976,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.1</v>
+        <v>23.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="H28" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="n">
         <v>2.8</v>
@@ -3070,19 +3070,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G30" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H30" t="n">
         <v>6.7</v>
@@ -3094,7 +3094,7 @@
         <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -3348,39 +3348,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.9</v>
+        <v>21.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.1</v>
+        <v>21.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -3524,16 +3524,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -3552,7 +3552,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.3</v>
+        <v>21.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.3</v>
+        <v>22.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="14">
@@ -3735,36 +3735,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K14" t="n">
         <v>2.3</v>
@@ -3821,36 +3821,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.2</v>
+        <v>21.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K16" t="n">
         <v>2.3</v>
@@ -3864,36 +3864,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G17" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="H17" t="n">
         <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
         <v>2.3</v>
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K20" t="n">
         <v>2.8</v>
-      </c>
-      <c r="G20" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4059,7 +4059,7 @@
         <v>7.8</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
         <v>1.6</v>
@@ -4083,23 +4083,23 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="H22" t="n">
         <v>4.8</v>
@@ -4111,7 +4111,7 @@
         <v>0.9</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="23">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4130,31 +4130,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>2.7</v>
       </c>
       <c r="G23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.4</v>
+        <v>26.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G24" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="H24" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K24" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="25">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4216,31 +4216,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>2.7</v>
       </c>
       <c r="G25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>26.2</v>
+        <v>23.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="I26" t="n">
         <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="27">
@@ -4470,26 +4470,26 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G31" t="n">
         <v>8.9</v>
       </c>
       <c r="H31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
@@ -4631,16 +4631,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G3" t="n">
         <v>10.5</v>
@@ -4765,17 +4765,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>1.3</v>
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.9</v>
+        <v>19.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>10.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H7" t="n">
         <v>3.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.9</v>
+        <v>20.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G8" t="n">
-        <v>9.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="H8" t="n">
         <v>3.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -5014,11 +5014,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5030,7 +5030,7 @@
         <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="H12" t="n">
         <v>4.5</v>
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="n">
         <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
         <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="18">
@@ -5362,19 +5362,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>2.4</v>
       </c>
       <c r="G20" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="H20" t="n">
         <v>4.2</v>
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.6</v>
+        <v>22.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>10.3</v>
+        <v>9.4</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G22" t="n">
-        <v>9.300000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.2</v>
+        <v>22.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22.9</v>
+        <v>24.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G27" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="K27" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="28">
@@ -5741,39 +5741,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.3</v>
+        <v>24.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="F29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G29" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1.9</v>
       </c>
     </row>
     <row r="30">
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.5</v>
+        <v>27.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="G30" t="n">
-        <v>12.4</v>
+        <v>10.8</v>
       </c>
       <c r="H30" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K30" t="n">
         <v>1.9</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="31">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5840,23 +5840,23 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G31" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="H31" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I31" t="n">
         <v>1.7</v>
       </c>
       <c r="J31" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="K31" t="n">
         <v>3.1</v>
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.3</v>
+        <v>19.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.7</v>
+        <v>21.3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.7</v>
+        <v>18.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J7" t="n">
         <v>1.4</v>
       </c>
-      <c r="G7" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.6</v>
-      </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.4</v>
+        <v>19.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -6242,36 +6242,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.1</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K9" t="n">
         <v>2.6</v>
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18.4</v>
+        <v>19.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>14.7</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19.8</v>
+        <v>19.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>13.3</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.9</v>
+        <v>19.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="G12" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G13" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>1.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20.7</v>
+        <v>21.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>12.2</v>
+        <v>13.6</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J15" t="n">
         <v>1.5</v>
       </c>
-      <c r="J15" t="n">
-        <v>1.9</v>
-      </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19.3</v>
+        <v>20.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
-        <v>14.6</v>
+        <v>12.4</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -6609,7 +6609,7 @@
         <v>15.6</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
         <v>1.3</v>
@@ -6618,7 +6618,7 @@
         <v>1.8</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -6633,23 +6633,23 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="H18" t="n">
         <v>4</v>
@@ -6658,7 +6658,7 @@
         <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="K18" t="n">
         <v>2.3</v>
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="H19" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G21" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.2</v>
+        <v>22.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="H22" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="K22" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.8</v>
+        <v>23.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J23" t="n">
         <v>1.5</v>
       </c>
-      <c r="G23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2.3</v>
-      </c>
       <c r="K23" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.6</v>
+        <v>21.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G24" t="n">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.9</v>
+        <v>24.5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G25" t="n">
-        <v>15.5</v>
+        <v>14.7</v>
       </c>
       <c r="H25" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -7063,23 +7063,23 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1.2</v>
       </c>
       <c r="G28" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="H28" t="n">
         <v>4.2</v>
@@ -7149,16 +7149,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -7171,13 +7171,13 @@
         <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>2.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -497,39 +497,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3">
@@ -540,15 +540,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -557,22 +557,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
         <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -591,12 +591,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.3</v>
+        <v>23</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>8.9</v>
+        <v>7.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.2</v>
+        <v>21.6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -768,14 +768,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
         <v>8.5</v>
@@ -845,11 +845,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
         <v>6.4</v>
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.1</v>
+        <v>25.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="H11" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12">
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -950,7 +950,7 @@
         <v>6.5</v>
       </c>
       <c r="H12" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I12" t="n">
         <v>1.8</v>
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.4</v>
+        <v>24.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26.5</v>
+        <v>23.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K14" t="n">
         <v>2.9</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.4</v>
       </c>
     </row>
     <row r="15">
@@ -1056,36 +1056,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25.8</v>
+        <v>23.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
         <v>3.6</v>
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.6</v>
+        <v>23</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H16" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="H17" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="18">
@@ -1185,20 +1185,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.7</v>
+        <v>26.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1208,13 +1208,13 @@
         <v>6.1</v>
       </c>
       <c r="H18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
         <v>3.4</v>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1241,17 +1241,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>3.3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I19" t="n">
         <v>1.7</v>
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.8</v>
+        <v>24.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="H20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
         <v>0.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="21">
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1404,35 +1404,35 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G23" t="n">
         <v>6.2</v>
       </c>
       <c r="H23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1509,10 +1509,10 @@
         <v>6.8</v>
       </c>
       <c r="H25" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.6</v>
+        <v>25.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="H26" t="n">
         <v>8.9</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1572,33 +1572,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="H27" t="n">
         <v>8.9</v>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
         <v>0.6</v>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1632,13 +1632,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H28" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I28" t="n">
         <v>2.6</v>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1881,7 +1881,7 @@
         <v>6.5</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.8</v>
+        <v>22.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -2034,11 +2034,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2053,7 +2053,7 @@
         <v>6.6</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I6" t="n">
         <v>1.6</v>
@@ -2148,7 +2148,7 @@
         <v>0.7</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="H9" t="n">
         <v>5.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.8</v>
+        <v>22.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -2249,16 +2249,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2301,17 +2301,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>3.6</v>
       </c>
       <c r="G12" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I12" t="n">
         <v>1.6</v>
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="H14" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H15" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="16">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.4</v>
+        <v>23.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G17" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="H17" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G18" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H18" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="H19" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="I19" t="n">
         <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="20">
@@ -2632,24 +2632,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.6</v>
+        <v>22</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
         <v>6.6</v>
@@ -2658,13 +2658,13 @@
         <v>5.8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -2769,31 +2769,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="G23" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H23" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2812,31 +2812,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G24" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H24" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2898,16 +2898,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G26" t="n">
         <v>6.7</v>
@@ -2916,7 +2916,7 @@
         <v>5.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0.6</v>
@@ -2941,22 +2941,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G27" t="n">
         <v>7.1</v>
       </c>
       <c r="H27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
         <v>1.8</v>
@@ -2980,20 +2980,20 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G28" t="n">
         <v>6.8</v>
@@ -3005,7 +3005,7 @@
         <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K28" t="n">
         <v>2.8</v>
@@ -3023,26 +3023,26 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H29" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I29" t="n">
         <v>2.1</v>
@@ -3062,30 +3062,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.1</v>
+        <v>24.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="G30" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="H30" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="I30" t="n">
         <v>1.9</v>
@@ -3094,7 +3094,7 @@
         <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="31">
@@ -3105,30 +3105,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.7</v>
+        <v>26.1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G31" t="n">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="H31" t="n">
-        <v>5.2</v>
+        <v>6.7</v>
       </c>
       <c r="I31" t="n">
         <v>1.9</v>
@@ -3137,7 +3137,7 @@
         <v>0.8</v>
       </c>
       <c r="K31" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -3223,23 +3223,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="H2" t="n">
         <v>3.9</v>
@@ -3266,11 +3266,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3309,26 +3309,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I4" t="n">
         <v>1.7</v>
@@ -3352,11 +3352,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3368,7 +3368,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="H5" t="n">
         <v>4.6</v>
@@ -3481,11 +3481,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
         <v>7.7</v>
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.9</v>
+        <v>21.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>7.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
         <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.3</v>
+        <v>22.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>8.300000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.3</v>
+        <v>23</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="G15" t="n">
-        <v>8.300000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="G16" t="n">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -3864,36 +3864,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.1</v>
+        <v>21.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K17" t="n">
         <v>2.3</v>
@@ -4001,19 +4001,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H20" t="n">
         <v>4.4</v>
@@ -4040,26 +4040,26 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3.3</v>
       </c>
       <c r="G21" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
         <v>1.6</v>
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.2</v>
+        <v>23.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -4130,31 +4130,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>2.7</v>
       </c>
       <c r="G23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.1</v>
+        <v>22.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G24" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="25">
@@ -4208,36 +4208,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.2</v>
+        <v>25.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="G25" t="n">
-        <v>8.800000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="H25" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I25" t="n">
         <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
         <v>2.6</v>
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="H26" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0.9</v>
       </c>
       <c r="K26" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -4302,31 +4302,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="H27" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0.9</v>
       </c>
       <c r="K27" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="28">
@@ -4337,39 +4337,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.7</v>
+        <v>24</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G28" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K28" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="29">
@@ -4380,39 +4380,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>8.9</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K29" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="30">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G30" t="n">
         <v>7.7</v>
@@ -4584,23 +4584,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="H2" t="n">
         <v>3.9</v>
@@ -4623,30 +4623,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.8</v>
+        <v>20.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>10.5</v>
+        <v>8.9</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="n">
         <v>1.5</v>
@@ -4655,7 +4655,7 @@
         <v>1.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="4">
@@ -4666,30 +4666,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.8</v>
+        <v>21.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>8.9</v>
+        <v>10.5</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>1.5</v>
@@ -4698,7 +4698,7 @@
         <v>1.2</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.8</v>
+        <v>20.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J5" t="n">
         <v>1.3</v>
       </c>
-      <c r="J5" t="n">
-        <v>1.6</v>
-      </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.3</v>
+        <v>19.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>10.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="7">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.9</v>
+        <v>21.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.9</v>
+        <v>22.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>10.2</v>
+        <v>10.7</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -4885,16 +4885,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4910,7 +4910,7 @@
         <v>0.9</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -4924,36 +4924,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
         <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>2.7</v>
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G11" t="n">
-        <v>9.4</v>
+        <v>10.1</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
         <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5023,14 +5023,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H12" t="n">
         <v>4.5</v>
@@ -5042,7 +5042,7 @@
         <v>1.8</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13">
@@ -5057,20 +5057,20 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="G13" t="n">
         <v>10.6</v>
@@ -5082,7 +5082,7 @@
         <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="K13" t="n">
         <v>2.4</v>
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G15" t="n">
         <v>10.7</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="16">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>22.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
         <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -5233,31 +5233,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.3</v>
+        <v>23.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="G18" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -5315,11 +5315,11 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>11.5</v>
+        <v>9.9</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>1.2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.5</v>
+        <v>23.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G21" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I21" t="n">
         <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.6</v>
+        <v>22.4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="n">
-        <v>10.3</v>
+        <v>9.4</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>22.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="H23" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J23" t="n">
         <v>1.6</v>
       </c>
-      <c r="J23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K23" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.1</v>
+        <v>23.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="G24" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G25" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="H25" t="n">
         <v>4.3</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>1.1</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="26">
@@ -5612,24 +5612,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G26" t="n">
         <v>9.699999999999999</v>
@@ -5638,13 +5638,13 @@
         <v>4.3</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="K26" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="27">
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.2</v>
+        <v>22.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H27" t="n">
         <v>4.4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -5702,20 +5702,20 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G28" t="n">
         <v>10.7</v>
@@ -5804,19 +5804,19 @@
         <v>2.6</v>
       </c>
       <c r="G30" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="H30" t="n">
         <v>4.4</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>1.3</v>
       </c>
       <c r="K30" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -5945,16 +5945,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.8</v>
+        <v>21.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>13.5</v>
+        <v>15.8</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>14.4</v>
+        <v>13.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
         <v>1.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5">
@@ -6121,19 +6121,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="H6" t="n">
         <v>4.5</v>
@@ -6145,7 +6145,7 @@
         <v>1.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18.5</v>
+        <v>19.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="G8" t="n">
-        <v>13.3</v>
+        <v>14.9</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.7</v>
+        <v>19.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G9" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J9" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.7</v>
+        <v>21.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19.1</v>
+        <v>21.7</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>67.6</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="G12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J12" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.9</v>
+        <v>18.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="G13" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="H13" t="n">
         <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>1.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>19.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I14" t="n">
         <v>1.3</v>
       </c>
-      <c r="G14" t="n">
-        <v>15</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.7</v>
-      </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.4</v>
+        <v>20.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I15" t="n">
         <v>1.5</v>
       </c>
-      <c r="G15" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.9</v>
+        <v>22.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G16" t="n">
-        <v>12.4</v>
+        <v>15</v>
       </c>
       <c r="H16" t="n">
         <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="17">
@@ -6586,36 +6586,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.9</v>
+        <v>21.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>15.6</v>
+        <v>11.6</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K17" t="n">
         <v>2.3</v>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -6637,31 +6637,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G18" t="n">
-        <v>11.6</v>
+        <v>13.7</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.7</v>
+        <v>20.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G19" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="20">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1.2</v>
       </c>
       <c r="G20" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
         <v>1.3</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1.2</v>
       </c>
       <c r="G21" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
         <v>1.3</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.9</v>
+        <v>21.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G23" t="n">
-        <v>15.5</v>
+        <v>14.3</v>
       </c>
       <c r="H23" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21.2</v>
+        <v>23.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>14.3</v>
+        <v>15.5</v>
       </c>
       <c r="H24" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="25">
@@ -6934,7 +6934,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6943,17 +6943,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G25" t="n">
         <v>14.7</v>
       </c>
       <c r="H25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
         <v>1.7</v>
@@ -6962,7 +6962,7 @@
         <v>2.8</v>
       </c>
       <c r="K25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -6977,23 +6977,23 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="H26" t="n">
         <v>3.6</v>
@@ -7020,11 +7020,11 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -7036,10 +7036,10 @@
         <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="H27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
         <v>1.6</v>
@@ -7067,22 +7067,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G28" t="n">
         <v>15.7</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I28" t="n">
         <v>1.4</v>
@@ -7110,19 +7110,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="H29" t="n">
         <v>4.5</v>
@@ -7196,12 +7196,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -7217,7 +7217,7 @@
         <v>1.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K31" t="n">
         <v>2.7</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -630,16 +630,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -658,7 +658,7 @@
         <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -744,7 +744,7 @@
         <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H12" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24.4</v>
+        <v>23.1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="H13" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K15" t="n">
         <v>2.9</v>
-      </c>
-      <c r="G15" t="n">
-        <v>6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.6</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>24.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="H16" t="n">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.7</v>
+        <v>23</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="H17" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.5</v>
+        <v>23.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="H19" t="n">
-        <v>8.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="20">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="22">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G22" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="H22" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K22" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.6</v>
+        <v>26</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="H23" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="24">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G24" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="H24" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="25">
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H26" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K28" t="n">
         <v>3</v>
-      </c>
-      <c r="G28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H28" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="29">
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1748,26 +1748,26 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.8</v>
+        <v>26.2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G31" t="n">
         <v>6.5</v>
       </c>
       <c r="H31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I31" t="n">
         <v>2.3</v>
@@ -1776,7 +1776,7 @@
         <v>0.7</v>
       </c>
       <c r="K31" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>
@@ -1862,16 +1862,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1905,20 +1905,20 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
         <v>6.4</v>
@@ -1987,36 +1987,36 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.5</v>
+        <v>22.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K5" t="n">
         <v>3.3</v>
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="H6" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H7" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I7" t="n">
         <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
         <v>0.7</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -2206,16 +2206,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2225,7 +2225,7 @@
         <v>6.6</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I10" t="n">
         <v>1.5</v>
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="H13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I13" t="n">
         <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.4</v>
+        <v>22.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G15" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="H15" t="n">
-        <v>6.1</v>
+        <v>5.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16">
@@ -2460,11 +2460,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,26 +2473,26 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G16" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.9</v>
+        <v>23.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="H18" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.3</v>
+        <v>23.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="H19" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2821,19 +2821,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G24" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H24" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I24" t="n">
         <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K24" t="n">
         <v>2.7</v>
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -3062,39 +3062,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.7</v>
+        <v>25.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="G30" t="n">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="H30" t="n">
-        <v>5.2</v>
+        <v>6.7</v>
       </c>
       <c r="I30" t="n">
         <v>1.9</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K30" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -3105,30 +3105,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.1</v>
+        <v>24.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="H31" t="n">
-        <v>6.7</v>
+        <v>5.2</v>
       </c>
       <c r="I31" t="n">
         <v>1.9</v>
@@ -3137,7 +3137,7 @@
         <v>0.8</v>
       </c>
       <c r="K31" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3282,7 +3282,7 @@
         <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H3" t="n">
         <v>3.8</v>
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.6</v>
+        <v>21.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -3626,7 +3626,7 @@
         <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H11" t="n">
         <v>4.5</v>
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K12" t="n">
         <v>3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -3778,36 +3778,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.1</v>
+        <v>21.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K15" t="n">
         <v>2.3</v>
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="G16" t="n">
-        <v>8.300000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.6</v>
+        <v>23.5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G17" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0.7</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.5</v>
+        <v>22.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G18" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="H18" t="n">
         <v>4.7</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G19" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K19" t="n">
         <v>2.8</v>
-      </c>
-      <c r="G19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="H22" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="23">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.2</v>
+        <v>23.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G24" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.9</v>
+        <v>22.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G25" t="n">
-        <v>7.3</v>
+        <v>8.6</v>
       </c>
       <c r="H25" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.3</v>
+        <v>25.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
         <v>7.3</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G27" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="H27" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0.9</v>
       </c>
       <c r="K27" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4627,11 +4627,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4652,7 +4652,7 @@
         <v>1.5</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
         <v>2.1</v>
@@ -4695,7 +4695,7 @@
         <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -4709,15 +4709,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.9</v>
+        <v>19.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4726,22 +4726,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>10.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="6">
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.9</v>
+        <v>22.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>9.300000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J6" t="n">
         <v>1.6</v>
       </c>
-      <c r="J6" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K6" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.3</v>
+        <v>20.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J7" t="n">
         <v>1.3</v>
       </c>
-      <c r="J7" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.8</v>
+        <v>21.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4894,17 +4894,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I9" t="n">
         <v>0.9</v>
@@ -4913,7 +4913,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="10">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>2.3</v>
       </c>
       <c r="G15" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.2</v>
+        <v>23.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>11.1</v>
+        <v>10.1</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
         <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
         <v>1.2</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.4</v>
+        <v>22.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G19" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="H19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="G20" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>1.2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.2</v>
+        <v>22.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
         <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G22" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I22" t="n">
         <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.2</v>
+        <v>23.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="G23" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.8</v>
+        <v>22.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="G24" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="H24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J24" t="n">
         <v>1.6</v>
       </c>
-      <c r="J24" t="n">
-        <v>1.3</v>
-      </c>
       <c r="K24" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -5754,14 +5754,14 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G29" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="H29" t="n">
         <v>4.5</v>
@@ -5773,7 +5773,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="30">
@@ -6031,26 +6031,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I4" t="n">
         <v>1.2</v>
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.6</v>
+        <v>19</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>14.9</v>
+        <v>13.9</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -6113,20 +6113,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -6136,16 +6136,16 @@
         <v>14.9</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
         <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.4</v>
+        <v>21.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="G9" t="n">
-        <v>13.2</v>
+        <v>14.9</v>
       </c>
       <c r="H9" t="n">
         <v>3.8</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -6332,7 +6332,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>67.6</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -6351,7 +6351,7 @@
         <v>13.7</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I11" t="n">
         <v>1.3</v>
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>19.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>13.9</v>
+        <v>13.3</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19.4</v>
+        <v>20.9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="G14" t="n">
-        <v>14.6</v>
+        <v>12.4</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20.9</v>
+        <v>19.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="G15" t="n">
-        <v>12.4</v>
+        <v>14.6</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.7</v>
+        <v>20.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="G18" t="n">
-        <v>13.7</v>
+        <v>15.6</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
         <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20.9</v>
+        <v>21.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G19" t="n">
-        <v>15.6</v>
+        <v>13.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
         <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -6805,16 +6805,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -6827,7 +6827,7 @@
         <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>2.3</v>
@@ -6848,35 +6848,35 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G23" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="H23" t="n">
         <v>3.8</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G24" t="n">
-        <v>15.5</v>
+        <v>14.7</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.8</v>
+        <v>23.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>14.7</v>
+        <v>15.5</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K25" t="n">
         <v>2.8</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="G27" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="K27" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="28">
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.8</v>
+        <v>23</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="G28" t="n">
-        <v>15.7</v>
+        <v>14.6</v>
       </c>
       <c r="H28" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K28" t="n">
         <v>2.3</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="29">
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7158,26 +7158,26 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="H30" t="n">
         <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>2.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="31">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -501,16 +501,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -520,7 +520,7 @@
         <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>1.5</v>
@@ -548,19 +548,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H3" t="n">
         <v>7.6</v>
@@ -587,23 +587,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H4" t="n">
         <v>7.5</v>
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23</v>
+        <v>21.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="H6" t="n">
-        <v>7.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.4</v>
+        <v>23.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -787,7 +787,7 @@
         <v>0.4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="9">
@@ -806,12 +806,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -821,7 +821,7 @@
         <v>6.3</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
@@ -849,7 +849,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -864,10 +864,10 @@
         <v>6.4</v>
       </c>
       <c r="H10" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
         <v>0.6</v>
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25.8</v>
+        <v>26.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G11" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="H11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I11" t="n">
         <v>1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="12">
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.4</v>
+        <v>25.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H12" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>1.9</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="13">
@@ -978,12 +978,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -993,7 +993,7 @@
         <v>5.5</v>
       </c>
       <c r="H13" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I13" t="n">
         <v>2</v>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1021,31 +1021,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K14" t="n">
         <v>2.9</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6</v>
-      </c>
-      <c r="H14" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.6</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.5</v>
+        <v>24.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H15" t="n">
-        <v>7.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.5</v>
+        <v>23.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="17">
@@ -1146,32 +1146,32 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2.8</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
         <v>2.8</v>
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.6</v>
+        <v>23.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="H18" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.7</v>
+        <v>24.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G19" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="H19" t="n">
-        <v>9.300000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="20">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1291,16 +1291,16 @@
         <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I20" t="n">
         <v>2.1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K20" t="n">
         <v>3.4</v>
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26</v>
+        <v>24.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G23" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="H23" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.6</v>
+        <v>26</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="H24" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="25">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="H27" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="28">
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="H29" t="n">
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K29" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K4" t="n">
         <v>3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.5</v>
+        <v>22.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I7" t="n">
         <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="G8" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
         <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.7</v>
+        <v>23.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.7</v>
+        <v>21.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="H12" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="I12" t="n">
         <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.3</v>
+        <v>22.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G13" t="n">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -2374,27 +2374,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H14" t="n">
         <v>5.2</v>
@@ -2403,10 +2403,10 @@
         <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="15">
@@ -2417,36 +2417,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.7</v>
+        <v>23.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>7.4</v>
+        <v>6.1</v>
       </c>
       <c r="H15" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
         <v>2.5</v>
@@ -2460,20 +2460,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.4</v>
+        <v>22.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -2483,16 +2483,16 @@
         <v>6.4</v>
       </c>
       <c r="H16" t="n">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -2507,16 +2507,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -2546,30 +2546,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G18" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H18" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I18" t="n">
         <v>1.9</v>
@@ -2578,7 +2578,7 @@
         <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G19" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H19" t="n">
         <v>6.1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4.8</v>
       </c>
       <c r="I19" t="n">
         <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>23.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H20" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="21">
@@ -2722,11 +2722,11 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G22" t="n">
         <v>6.6</v>
       </c>
       <c r="H22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I22" t="n">
         <v>1.4</v>
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>3.5</v>
       </c>
       <c r="G24" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="H24" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.9</v>
+        <v>23.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="G25" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H25" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.4</v>
+        <v>24.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G26" t="n">
         <v>6.7</v>
@@ -2916,13 +2916,13 @@
         <v>5.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="27">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2965,7 +2965,7 @@
         <v>0.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="28">
@@ -2989,11 +2989,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G28" t="n">
         <v>6.8</v>
@@ -3027,12 +3027,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -3223,23 +3223,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="H2" t="n">
         <v>3.9</v>
@@ -3309,23 +3309,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H4" t="n">
         <v>3.9</v>
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.9</v>
+        <v>22.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K6" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K7" t="n">
         <v>2.9</v>
-      </c>
-      <c r="G7" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.6</v>
+        <v>22.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -3606,11 +3606,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.2</v>
+        <v>21.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3619,26 +3619,26 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>6.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.6</v>
+        <v>22.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J12" t="n">
         <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>21.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.9</v>
+        <v>23</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K14" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.3</v>
       </c>
     </row>
     <row r="15">
@@ -3778,36 +3778,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G15" t="n">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K15" t="n">
         <v>2.3</v>
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -4040,20 +4040,20 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G21" t="n">
         <v>7.7</v>
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K23" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.1</v>
+        <v>22.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K24" t="n">
         <v>2.8</v>
-      </c>
-      <c r="G24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H24" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.2</v>
+        <v>23.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H25" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.9</v>
+        <v>23.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.3</v>
+        <v>25.7</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
         <v>7.3</v>
       </c>
       <c r="H27" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28">
@@ -4380,39 +4380,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
       <c r="H29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4489,7 +4489,7 @@
         <v>8.9</v>
       </c>
       <c r="H31" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
@@ -4588,19 +4588,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H2" t="n">
         <v>3.9</v>
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.8</v>
+        <v>20.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="I6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J6" t="n">
         <v>1.3</v>
       </c>
-      <c r="J6" t="n">
-        <v>1.6</v>
-      </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -4838,20 +4838,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4861,16 +4861,16 @@
         <v>10.8</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
         <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -4932,19 +4932,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="H10" t="n">
         <v>4.3</v>
@@ -4956,7 +4956,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -4971,20 +4971,20 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G11" t="n">
         <v>10.1</v>
@@ -4999,7 +4999,7 @@
         <v>1.3</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -5014,16 +5014,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K15" t="n">
         <v>2.8</v>
@@ -5186,16 +5186,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>11.1</v>
+        <v>10.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>22.2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K19" t="n">
         <v>2.4</v>
-      </c>
-      <c r="G19" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
         <v>4.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="23">
@@ -5491,16 +5491,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G23" t="n">
         <v>10.4</v>
@@ -5512,7 +5512,7 @@
         <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K23" t="n">
         <v>2.4</v>
@@ -5530,23 +5530,23 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2.8</v>
       </c>
       <c r="G24" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="H24" t="n">
         <v>4</v>
@@ -5558,7 +5558,7 @@
         <v>1.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>23.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="H25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K25" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.5</v>
+        <v>23.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G26" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="H26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>1.1</v>
       </c>
       <c r="K26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="27">
@@ -5702,20 +5702,20 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G28" t="n">
         <v>10.7</v>
@@ -5745,16 +5745,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -5767,13 +5767,13 @@
         <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="30">
@@ -5788,11 +5788,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27.3</v>
+        <v>27.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5804,10 +5804,10 @@
         <v>2.6</v>
       </c>
       <c r="G30" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="H30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I30" t="n">
         <v>1.4</v>
@@ -5945,16 +5945,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -5964,7 +5964,7 @@
         <v>13.4</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I2" t="n">
         <v>1.7</v>
@@ -5973,7 +5973,7 @@
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>13.9</v>
+        <v>14.9</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -6117,16 +6117,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -6142,10 +6142,10 @@
         <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.3</v>
+        <v>19.6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -6203,11 +6203,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -6219,7 +6219,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="H8" t="n">
         <v>2.9</v>
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>1.3</v>
       </c>
       <c r="G9" t="n">
-        <v>14.9</v>
+        <v>13.9</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
@@ -6289,26 +6289,26 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
         <v>1.2</v>
@@ -6418,23 +6418,23 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>0.7</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="H13" t="n">
         <v>3.6</v>
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19.4</v>
+        <v>22.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="G15" t="n">
-        <v>14.6</v>
+        <v>15.1</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.1</v>
+        <v>19.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="G16" t="n">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="17">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -6594,31 +6594,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G17" t="n">
-        <v>11.6</v>
+        <v>13.7</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -6629,36 +6629,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20.8</v>
+        <v>21.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="G18" t="n">
-        <v>15.6</v>
+        <v>11.6</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K18" t="n">
         <v>2.3</v>
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.7</v>
+        <v>20.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="G19" t="n">
-        <v>13.7</v>
+        <v>15.6</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
         <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="20">
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G20" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="H20" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I20" t="n">
         <v>1.3</v>
@@ -6747,7 +6747,7 @@
         <v>1.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -6762,16 +6762,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.8</v>
+        <v>23.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>14.7</v>
+        <v>15.5</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K24" t="n">
         <v>2.8</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G25" t="n">
-        <v>15.5</v>
+        <v>14.7</v>
       </c>
       <c r="H25" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -6973,39 +6973,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22</v>
+        <v>23.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1</v>
+        <v>15.7</v>
       </c>
       <c r="H26" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K26" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="27">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.8</v>
+        <v>23</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>15.7</v>
+        <v>14.6</v>
       </c>
       <c r="H27" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K27" t="n">
         <v>2.3</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="28">
@@ -7059,36 +7059,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23</v>
+        <v>22.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>14.6</v>
+        <v>14.1</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
         <v>2.3</v>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -7153,19 +7153,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="H30" t="n">
         <v>4.5</v>
@@ -7196,7 +7196,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -7211,13 +7211,13 @@
         <v>15.8</v>
       </c>
       <c r="H31" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K31" t="n">
         <v>2.7</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -510,20 +510,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G2" t="n">
         <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
@@ -587,29 +587,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H4" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
         <v>0.6</v>
@@ -673,11 +673,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -689,10 +689,10 @@
         <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>1.5</v>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -725,17 +725,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H7" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I7" t="n">
         <v>1.8</v>
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26.6</v>
+        <v>22.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="H11" t="n">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.1</v>
+        <v>26.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="H13" t="n">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.6</v>
+        <v>24.2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H14" t="n">
-        <v>7.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24.2</v>
+        <v>23.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G16" t="n">
         <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -1142,15 +1142,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1159,22 +1159,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="H17" t="n">
-        <v>9.4</v>
+        <v>7.3</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="18">
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1251,7 +1251,7 @@
         <v>6.6</v>
       </c>
       <c r="H19" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I19" t="n">
         <v>1.7</v>
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G22" t="n">
         <v>6.2</v>
       </c>
       <c r="H22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I22" t="n">
         <v>2.1</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G23" t="n">
         <v>6.2</v>
       </c>
       <c r="H23" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
         <v>2.1</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="24">
@@ -1490,11 +1490,11 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1509,10 +1509,10 @@
         <v>6.8</v>
       </c>
       <c r="H25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.6</v>
+        <v>24.9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="H27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="H28" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="29">
@@ -1705,20 +1705,20 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G30" t="n">
         <v>6.5</v>
@@ -1730,10 +1730,10 @@
         <v>2.1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="31">
@@ -1748,26 +1748,26 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G31" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H31" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>2.3</v>
@@ -1776,7 +1776,7 @@
         <v>0.7</v>
       </c>
       <c r="K31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -1862,11 +1862,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1901,39 +1901,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.6</v>
+        <v>22.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.6</v>
+        <v>21.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5">
@@ -2116,36 +2116,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="n">
-        <v>6.7</v>
+        <v>6.1</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="I8" t="n">
         <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K8" t="n">
         <v>3.3</v>
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10">
@@ -2249,16 +2249,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.8</v>
+        <v>23.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2339,31 +2339,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="H13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="H14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G16" t="n">
         <v>6.4</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="I16" t="n">
         <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="17">
@@ -2503,27 +2503,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.4</v>
+        <v>22</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H17" t="n">
         <v>5.7</v>
@@ -2535,7 +2535,7 @@
         <v>0.7</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18">
@@ -2546,11 +2546,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2559,26 +2559,26 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G18" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H18" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="19">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2597,31 +2597,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="H19" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="20">
@@ -2632,30 +2632,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I20" t="n">
         <v>1.9</v>
@@ -2664,7 +2664,7 @@
         <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
@@ -2722,16 +2722,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2765,23 +2765,23 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>3.1</v>
       </c>
       <c r="G23" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H23" t="n">
         <v>5.3</v>
@@ -2790,7 +2790,7 @@
         <v>2.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K23" t="n">
         <v>3.2</v>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.1</v>
+        <v>23.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>3.3</v>
       </c>
       <c r="G27" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K27" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.3</v>
+        <v>24.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3.3</v>
       </c>
       <c r="G28" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="H28" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="29">
@@ -3066,16 +3066,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -3085,7 +3085,7 @@
         <v>6.7</v>
       </c>
       <c r="H30" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="I30" t="n">
         <v>1.9</v>
@@ -3094,7 +3094,7 @@
         <v>0.7</v>
       </c>
       <c r="K30" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31">
@@ -3109,23 +3109,23 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G31" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="H31" t="n">
         <v>5.2</v>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3285,7 +3285,7 @@
         <v>8.1</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
         <v>1.2</v>
@@ -3348,39 +3348,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
         <v>1.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.4</v>
+        <v>20.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="H6" t="n">
         <v>4.5</v>
@@ -3420,10 +3420,10 @@
         <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.6</v>
+        <v>22.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.2</v>
+        <v>20.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
         <v>2.8</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -3649,36 +3649,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.1</v>
+        <v>21.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K12" t="n">
         <v>2.3</v>
@@ -3692,36 +3692,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G13" t="n">
-        <v>7.7</v>
+        <v>6.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
         <v>2.3</v>
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>21.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="n">
         <v>7.1</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.9</v>
+        <v>22.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K16" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -3927,10 +3927,10 @@
         <v>3.3</v>
       </c>
       <c r="G18" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I18" t="n">
         <v>1.8</v>
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G23" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.2</v>
+        <v>23.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="H24" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="25">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.2</v>
+        <v>22.3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>2.7</v>
       </c>
       <c r="G25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H25" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.5</v>
+        <v>25.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="H26" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25.7</v>
+        <v>23.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G27" t="n">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K27" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="28">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4360,7 +4360,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I28" t="n">
         <v>1.8</v>
@@ -4427,26 +4427,26 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
         <v>7.7</v>
       </c>
       <c r="H30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I30" t="n">
         <v>1.8</v>
@@ -4455,7 +4455,7 @@
         <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -4584,11 +4584,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4600,10 +4600,10 @@
         <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -4623,30 +4623,30 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.6</v>
+        <v>21.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G3" t="n">
-        <v>8.9</v>
+        <v>10.5</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>1.5</v>
@@ -4655,7 +4655,7 @@
         <v>1.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -4666,30 +4666,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.8</v>
+        <v>20.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="G4" t="n">
-        <v>10.5</v>
+        <v>8.9</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
         <v>1.5</v>
@@ -4698,7 +4698,7 @@
         <v>1.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5">
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -4735,7 +4735,7 @@
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
         <v>1.1</v>
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.9</v>
+        <v>22.3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="H6" t="n">
         <v>3.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.7</v>
+        <v>20.9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="G9" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
         <v>9.5</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I11" t="n">
         <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.4</v>
+        <v>23.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="G12" t="n">
         <v>10.6</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J12" t="n">
         <v>1.4</v>
       </c>
-      <c r="J12" t="n">
-        <v>1.8</v>
-      </c>
       <c r="K12" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.2</v>
+        <v>21.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="G13" t="n">
         <v>10.6</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
         <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>1.1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>2.3</v>
       </c>
       <c r="G15" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="16">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.8</v>
+        <v>22.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G18" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I18" t="n">
         <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="19">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>1.2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="21">
@@ -5397,30 +5397,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
         <v>1.6</v>
@@ -5429,7 +5429,7 @@
         <v>1.2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="G22" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="H22" t="n">
         <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G23" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="H23" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="24">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5678,7 +5678,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I27" t="n">
         <v>1.8</v>
@@ -5687,7 +5687,7 @@
         <v>1.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="28">
@@ -5702,16 +5702,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.2</v>
+        <v>26.1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>2.9</v>
       </c>
       <c r="G31" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="H31" t="n">
         <v>5.4</v>
@@ -5856,7 +5856,7 @@
         <v>1.7</v>
       </c>
       <c r="J31" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="K31" t="n">
         <v>3.1</v>
@@ -5941,39 +5941,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G2" t="n">
-        <v>13.4</v>
+        <v>15</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.6</v>
+        <v>18.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>15.8</v>
+        <v>13.4</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6074,23 +6074,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>21.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="H5" t="n">
         <v>4.4</v>
@@ -6099,7 +6099,7 @@
         <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>3.3</v>
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.6</v>
+        <v>19.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -6242,36 +6242,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>13.9</v>
+        <v>14.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="K9" t="n">
         <v>2.6</v>
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>19.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I10" t="n">
         <v>1.5</v>
       </c>
-      <c r="G10" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K10" t="n">
         <v>2.2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19.7</v>
+        <v>18.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G12" t="n">
-        <v>13.3</v>
+        <v>13.9</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
         <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18.5</v>
+        <v>22.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="G13" t="n">
-        <v>13.9</v>
+        <v>15.1</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="14">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.3</v>
+        <v>19.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I15" t="n">
         <v>1.3</v>
       </c>
-      <c r="G15" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.7</v>
-      </c>
       <c r="J15" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="G16" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
         <v>1.3</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" t="n">
         <v>1.4</v>
       </c>
-      <c r="G17" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -6629,36 +6629,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.7</v>
+        <v>20.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="G18" t="n">
-        <v>11.6</v>
+        <v>15.6</v>
       </c>
       <c r="H18" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="K18" t="n">
         <v>2.3</v>
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -6805,23 +6805,23 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G22" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="H22" t="n">
         <v>4</v>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="H23" t="n">
         <v>3.8</v>
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G24" t="n">
-        <v>15.5</v>
+        <v>14.7</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.8</v>
+        <v>24.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
         <v>1.6</v>
       </c>
-      <c r="G25" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="H25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>2.8</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -6973,39 +6973,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.8</v>
+        <v>23</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="G26" t="n">
-        <v>15.7</v>
+        <v>14.6</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I26" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K26" t="n">
         <v>2.3</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="27">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="G27" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="K27" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="28">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -563,7 +563,7 @@
         <v>5.7</v>
       </c>
       <c r="H3" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="I3" t="n">
         <v>2.3</v>
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.7</v>
+        <v>21.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H5" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.5</v>
+        <v>23.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="H6" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.1</v>
+        <v>22</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G7" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -755,39 +755,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H8" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
@@ -802,16 +802,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -830,7 +830,7 @@
         <v>0.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -845,16 +845,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.9</v>
+        <v>25.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="H11" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
         <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="12">
@@ -927,27 +927,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.7</v>
+        <v>24.2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="H12" t="n">
         <v>8.699999999999999</v>
@@ -956,10 +956,10 @@
         <v>1.9</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13">
@@ -974,11 +974,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1013,11 +1013,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.2</v>
+        <v>23.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1026,26 +1026,26 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="H14" t="n">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="H15" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -1103,16 +1103,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1150,31 +1150,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G17" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="18">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1236,31 +1236,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G19" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="H19" t="n">
-        <v>8.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="20">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1279,31 +1279,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H20" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="21">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1346,7 +1346,7 @@
         <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -1404,11 +1404,11 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1426,7 +1426,7 @@
         <v>8</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0.5</v>
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26</v>
+        <v>25.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1463,19 +1463,19 @@
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H24" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I24" t="n">
         <v>1.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="25">
@@ -1486,39 +1486,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.8</v>
+        <v>24.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
         <v>8.9</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="26">
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.8</v>
+        <v>25.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G26" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="H26" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="27">
@@ -1576,26 +1576,26 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>6.5</v>
       </c>
       <c r="H27" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="I27" t="n">
         <v>2.4</v>
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="H28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="29">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G29" t="n">
         <v>5.7</v>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1767,7 +1767,7 @@
         <v>6.4</v>
       </c>
       <c r="H31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I31" t="n">
         <v>2.3</v>
@@ -1776,7 +1776,7 @@
         <v>0.7</v>
       </c>
       <c r="K31" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>
@@ -1901,39 +1901,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.6</v>
+        <v>21.9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K3" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.6</v>
+        <v>23.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5">
@@ -1991,16 +1991,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -2010,7 +2010,7 @@
         <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I5" t="n">
         <v>1.7</v>
@@ -2038,19 +2038,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H6" t="n">
         <v>5.4</v>
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G8" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
         <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H9" t="n">
         <v>5.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
         <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2288,33 +2288,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.6</v>
+        <v>22.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1</v>
+        <v>7.3</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>0.6</v>
@@ -2374,33 +2374,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.8</v>
+        <v>23.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0.6</v>
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="I15" t="n">
         <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>3.5</v>
       </c>
       <c r="G16" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H16" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
         <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>23.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G17" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H17" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.4</v>
+        <v>22</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="G18" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H18" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="19">
@@ -2593,16 +2593,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -2621,7 +2621,7 @@
         <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="20">
@@ -2636,16 +2636,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -2804,33 +2804,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>3.5</v>
       </c>
       <c r="G24" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H24" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.8</v>
+        <v>24.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="G25" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H25" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -2890,24 +2890,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.9</v>
+        <v>23.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="G26" t="n">
         <v>6.7</v>
@@ -2916,13 +2916,13 @@
         <v>5.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="27">
@@ -2937,23 +2937,23 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>3.3</v>
       </c>
       <c r="G27" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H27" t="n">
         <v>6.1</v>
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.1</v>
+        <v>24.7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="29">
@@ -3019,39 +3019,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.8</v>
+        <v>24.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G29" t="n">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="H29" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K29" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="30">
@@ -3075,14 +3075,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>3.8</v>
       </c>
       <c r="G30" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H30" t="n">
         <v>6.6</v>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H5" t="n">
         <v>4.5</v>
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.9</v>
+        <v>21.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
         <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>20.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3477,36 +3477,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="n">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
         <v>2.4</v>
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.1</v>
+        <v>21.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.6</v>
+        <v>21.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -3606,36 +3606,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
         <v>2.2</v>
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.6</v>
+        <v>21.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G15" t="n">
-        <v>7.8</v>
+        <v>6.7</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
         <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -3825,20 +3825,20 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G16" t="n">
         <v>7.1</v>
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.5</v>
+        <v>22.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G17" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.7</v>
+        <v>23.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -3954,23 +3954,23 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G19" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H19" t="n">
         <v>4.2</v>
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="H23" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="I23" t="n">
         <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.2</v>
+        <v>22.3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G24" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="H24" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K24" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="25">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.3</v>
+        <v>23.3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>2.7</v>
       </c>
       <c r="G25" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -4255,11 +4255,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4274,10 +4274,10 @@
         <v>7.3</v>
       </c>
       <c r="H26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0.7</v>
@@ -4302,28 +4302,28 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
         <v>8.9</v>
       </c>
       <c r="H27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I27" t="n">
         <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K27" t="n">
         <v>2.7</v>
@@ -4384,20 +4384,20 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G29" t="n">
         <v>7.4</v>
@@ -4470,23 +4470,23 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3.3</v>
       </c>
       <c r="G31" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H31" t="n">
         <v>4.6</v>
@@ -4627,20 +4627,20 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G3" t="n">
         <v>10.5</v>
@@ -4655,7 +4655,7 @@
         <v>1.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
@@ -4670,29 +4670,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G4" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="n">
         <v>1.1</v>
@@ -4795,36 +4795,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.4</v>
+        <v>20.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J7" t="n">
         <v>1.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.2</v>
       </c>
       <c r="K7" t="n">
         <v>2.9</v>
@@ -4881,36 +4881,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>10.3</v>
+        <v>10.8</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K9" t="n">
         <v>2.9</v>
@@ -4971,23 +4971,23 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H11" t="n">
         <v>4.3</v>
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="G12" t="n">
         <v>10.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -5057,16 +5057,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.7</v>
+        <v>23.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
         <v>10.6</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G15" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="16">
@@ -5182,11 +5182,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5195,26 +5195,26 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="H16" t="n">
         <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G18" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="H18" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
         <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G19" t="n">
-        <v>9.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="G21" t="n">
         <v>10.4</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>1.2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="G22" t="n">
         <v>10.4</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>1.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="23">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.3</v>
+        <v>23.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K24" t="n">
         <v>2.8</v>
-      </c>
-      <c r="G24" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H24" t="n">
-        <v>4</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G25" t="n">
-        <v>11.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.8</v>
+        <v>22.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="G26" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22.8</v>
+        <v>24</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G27" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K27" t="n">
         <v>2.3</v>
-      </c>
-      <c r="G27" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="H27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="28">
@@ -5741,39 +5741,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.7</v>
+        <v>26.9</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="G29" t="n">
-        <v>12.3</v>
+        <v>10.9</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K29" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27.1</v>
+        <v>24.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G30" t="n">
-        <v>10.9</v>
+        <v>12.3</v>
       </c>
       <c r="H30" t="n">
         <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31">
@@ -5831,32 +5831,32 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>2.9</v>
       </c>
       <c r="G31" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H31" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I31" t="n">
         <v>1.7</v>
       </c>
       <c r="J31" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="K31" t="n">
         <v>3.1</v>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6004,7 +6004,7 @@
         <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="H3" t="n">
         <v>3.3</v>
@@ -6070,30 +6070,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.3</v>
+        <v>21.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
         <v>1.3</v>
@@ -6102,7 +6102,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -6113,30 +6113,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
         <v>1.3</v>
@@ -6145,7 +6145,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -6160,16 +6160,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -6179,7 +6179,7 @@
         <v>14.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>1.2</v>
@@ -6188,7 +6188,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.1</v>
+        <v>19.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J8" t="n">
         <v>1.4</v>
       </c>
-      <c r="G8" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.9</v>
-      </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.9</v>
+        <v>19.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11">
@@ -6332,16 +6332,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18.5</v>
+        <v>20.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
-        <v>13.9</v>
+        <v>12.4</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.3</v>
+        <v>19.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="G13" t="n">
-        <v>15.1</v>
+        <v>14.7</v>
       </c>
       <c r="H13" t="n">
         <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20.9</v>
+        <v>18.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="G14" t="n">
-        <v>12.4</v>
+        <v>13.9</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="n">
         <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>19.4</v>
+        <v>22.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="G15" t="n">
-        <v>14.6</v>
+        <v>15.1</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
         <v>1.4</v>
       </c>
-      <c r="G16" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J16" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="G17" t="n">
-        <v>11.5</v>
+        <v>13.7</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1.1</v>
       </c>
       <c r="G18" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
         <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G19" t="n">
-        <v>15.8</v>
+        <v>15.4</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="20">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="G20" t="n">
-        <v>15.4</v>
+        <v>14.1</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -6766,19 +6766,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1.2</v>
       </c>
       <c r="G21" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="H21" t="n">
         <v>4.6</v>
@@ -6787,7 +6787,7 @@
         <v>1.3</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K21" t="n">
         <v>2.4</v>
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.7</v>
+        <v>21.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I22" t="n">
         <v>1.4</v>
       </c>
-      <c r="G22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J22" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="K22" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.6</v>
+        <v>22.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
         <v>1.3</v>
       </c>
-      <c r="G23" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.6</v>
-      </c>
       <c r="J23" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="24">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G25" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="H25" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26">
@@ -6973,39 +6973,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23</v>
+        <v>24.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
         <v>1.6</v>
       </c>
-      <c r="G26" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.6</v>
-      </c>
       <c r="K26" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="27">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.8</v>
+        <v>22.9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>15.7</v>
+        <v>14.7</v>
       </c>
       <c r="H27" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="28">
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -7072,23 +7072,23 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="H28" t="n">
         <v>3.6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K28" t="n">
         <v>2.3</v>
@@ -7106,23 +7106,23 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="H29" t="n">
         <v>4.5</v>
@@ -7134,7 +7134,7 @@
         <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -7165,19 +7165,19 @@
         <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>16.1</v>
+        <v>16.4</v>
       </c>
       <c r="H30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I30" t="n">
         <v>1.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K30" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="31">
@@ -7192,32 +7192,32 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.4</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1.2</v>
       </c>
       <c r="G31" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="H31" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I31" t="n">
         <v>1.9</v>
       </c>
       <c r="J31" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K31" t="n">
         <v>2.7</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -510,26 +510,26 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>2.9</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H2" t="n">
         <v>8.6</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.5</v>
+        <v>23.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="H5" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="H6" t="n">
         <v>7.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>21.6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H7" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -755,39 +755,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.8</v>
+        <v>22</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K8" t="n">
         <v>3.1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.4</v>
       </c>
     </row>
     <row r="9">
@@ -811,14 +811,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.1</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H9" t="n">
         <v>7.1</v>
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.8</v>
+        <v>25.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H10" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="11">
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25.6</v>
+        <v>22.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H11" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="12">
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.2</v>
+        <v>22.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="H12" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26.5</v>
+        <v>23.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="H13" t="n">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="I13" t="n">
         <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.5</v>
+        <v>26.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H14" t="n">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="I14" t="n">
         <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>24.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H16" t="n">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
         <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="17">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1236,31 +1236,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="H19" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="20">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1279,31 +1279,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="H20" t="n">
-        <v>8.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
         <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="21">
@@ -1318,16 +1318,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1337,7 +1337,7 @@
         <v>5.5</v>
       </c>
       <c r="H21" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I21" t="n">
         <v>1.9</v>
@@ -1346,7 +1346,7 @@
         <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="22">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1380,7 +1380,7 @@
         <v>6.2</v>
       </c>
       <c r="H22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>2.1</v>
@@ -1486,39 +1486,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.4</v>
+        <v>25.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H25" t="n">
         <v>8.9</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.8</v>
+        <v>24.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="G26" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H26" t="n">
         <v>8.9</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="27">
@@ -1619,16 +1619,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1862,11 +1862,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G2" t="n">
         <v>6.5</v>
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1927,7 +1927,7 @@
         <v>4.8</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0.6</v>
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.2</v>
+        <v>22.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -2077,16 +2077,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -2102,7 +2102,7 @@
         <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
         <v>3.4</v>
@@ -2163,26 +2163,26 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I9" t="n">
         <v>1.5</v>
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.6</v>
+        <v>23.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K11" t="n">
         <v>3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -2288,30 +2288,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I12" t="n">
         <v>1.6</v>
@@ -2320,7 +2320,7 @@
         <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="G13" t="n">
-        <v>6.4</v>
+        <v>7.3</v>
       </c>
       <c r="H13" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.6</v>
+        <v>23.2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.2</v>
+        <v>22.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
         <v>6.4</v>
       </c>
       <c r="H15" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="I15" t="n">
         <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H17" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="I17" t="n">
         <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>23.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="G18" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H18" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="I18" t="n">
         <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="H19" t="n">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.1</v>
+        <v>24.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G20" t="n">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="H20" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>23.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="H21" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="22">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G23" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G24" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="H24" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="25">
@@ -2851,20 +2851,20 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G25" t="n">
         <v>6.7</v>
@@ -2876,7 +2876,7 @@
         <v>1.5</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K25" t="n">
         <v>3.1</v>
@@ -2890,33 +2890,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3.5</v>
       </c>
       <c r="G26" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H26" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
         <v>0.6</v>
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.7</v>
+        <v>24.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="H28" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="29">
@@ -3019,39 +3019,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.1</v>
+        <v>24.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K29" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="30">
@@ -3223,16 +3223,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3242,7 +3242,7 @@
         <v>7.8</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -3266,26 +3266,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I3" t="n">
         <v>1.2</v>
@@ -3356,19 +3356,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="H5" t="n">
         <v>4.5</v>
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.9</v>
+        <v>20.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
         <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.9</v>
+        <v>21.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I7" t="n">
         <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.1</v>
+        <v>21.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -3520,30 +3520,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
@@ -3552,7 +3552,7 @@
         <v>0.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.3</v>
+        <v>22.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>8.300000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -3606,36 +3606,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K11" t="n">
         <v>2.2</v>
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.5</v>
+        <v>21.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I13" t="n">
         <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
@@ -3735,36 +3735,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2.5</v>
       </c>
       <c r="G14" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
         <v>2.3</v>
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.9</v>
+        <v>22.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.5</v>
+        <v>22.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
         <v>0.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -3963,11 +3963,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
         <v>8.4</v>
@@ -3993,33 +3993,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0.8</v>
@@ -4036,39 +4036,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
         <v>7.7</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
         <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.9</v>
+        <v>23.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H22" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23">
@@ -4169,11 +4169,11 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4197,7 +4197,7 @@
         <v>0.9</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -4674,19 +4674,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -4713,23 +4713,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="7">
@@ -4799,16 +4799,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4818,7 +4818,7 @@
         <v>10.3</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
         <v>1.5</v>
@@ -4838,20 +4838,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.7</v>
+        <v>21.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -4861,16 +4861,16 @@
         <v>10.8</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -4881,20 +4881,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.4</v>
+        <v>22.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -4904,16 +4904,16 @@
         <v>10.8</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
         <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K10" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4999,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.7</v>
+        <v>21.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
         <v>10.6</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.5</v>
+        <v>23.1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
         <v>10.6</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J13" t="n">
         <v>1.4</v>
       </c>
-      <c r="J13" t="n">
-        <v>1.8</v>
-      </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="G14" t="n">
         <v>10.6</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G15" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
         <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="16">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G16" t="n">
-        <v>10.2</v>
+        <v>10.7</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
         <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="17">
@@ -5225,36 +5225,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="G17" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K17" t="n">
         <v>2.7</v>
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -5311,11 +5311,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5324,26 +5324,26 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.6</v>
+        <v>22.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>10.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -5440,36 +5440,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K22" t="n">
         <v>2.5</v>
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="G23" t="n">
-        <v>9.6</v>
+        <v>11.6</v>
       </c>
       <c r="H23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.2</v>
+        <v>23.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2.4</v>
       </c>
       <c r="G24" t="n">
-        <v>11.4</v>
+        <v>10.4</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>1.2</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -6031,32 +6031,32 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G4" t="n">
         <v>13.5</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
         <v>1.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="K4" t="n">
         <v>2.7</v>
@@ -6074,16 +6074,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -6093,7 +6093,7 @@
         <v>14.9</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
         <v>1.3</v>
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.9</v>
+        <v>20.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>13.2</v>
+        <v>14.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>19.9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K9" t="n">
         <v>2.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.1</v>
+        <v>22</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.9</v>
+        <v>19.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20.8</v>
+        <v>18.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="G12" t="n">
-        <v>12.4</v>
+        <v>13.9</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19.3</v>
+        <v>21.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="G13" t="n">
-        <v>14.7</v>
+        <v>11.5</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K13" t="n">
         <v>2.3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18.7</v>
+        <v>19.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G14" t="n">
-        <v>13.9</v>
+        <v>14.7</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -6543,11 +6543,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.6</v>
+        <v>20.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -6556,23 +6556,23 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
-        <v>11.5</v>
+        <v>12.6</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="K16" t="n">
         <v>2.4</v>
@@ -6629,20 +6629,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -6652,16 +6652,16 @@
         <v>15.4</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
         <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -6672,30 +6672,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20.8</v>
+        <v>21.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1.1</v>
       </c>
       <c r="G19" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
         <v>1.3</v>
@@ -6704,7 +6704,7 @@
         <v>1.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -6715,36 +6715,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1.3</v>
       </c>
       <c r="G20" t="n">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="H20" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K20" t="n">
         <v>2.4</v>
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.6</v>
+        <v>22.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G21" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
         <v>1.3</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="22">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G23" t="n">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="K23" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="24">
@@ -6891,16 +6891,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -6910,16 +6910,16 @@
         <v>14.7</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I24" t="n">
         <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.8</v>
+        <v>24.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -6973,39 +6973,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G26" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J26" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="K26" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="27">
@@ -7110,22 +7110,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
         <v>1.6</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -563,7 +563,7 @@
         <v>5.7</v>
       </c>
       <c r="H3" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
         <v>2.3</v>
@@ -596,17 +596,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="I4" t="n">
         <v>1.7</v>
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="H5" t="n">
         <v>7.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
@@ -669,36 +669,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.7</v>
+        <v>23.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
         <v>7.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K6" t="n">
         <v>3.4</v>
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="G7" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -755,39 +755,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>21.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="H8" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -854,7 +854,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -867,7 +867,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0.4</v>
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I11" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -927,7 +927,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -935,31 +935,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="H12" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>2.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.3</v>
+        <v>26.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26.5</v>
+        <v>22.9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="H14" t="n">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
         <v>0.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -1146,16 +1146,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1165,10 +1165,10 @@
         <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
         <v>0.6</v>
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.8</v>
+        <v>24.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G18" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="H18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="19">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1236,31 +1236,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="H19" t="n">
-        <v>8.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.7</v>
+        <v>23.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="H20" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="21">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1322,31 +1322,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="H21" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="22">
@@ -1361,26 +1361,26 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3.4</v>
       </c>
       <c r="G22" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="H22" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I22" t="n">
         <v>2.1</v>
@@ -1404,35 +1404,35 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>3.1</v>
       </c>
       <c r="G23" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="H23" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="24">
@@ -1486,39 +1486,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.8</v>
+        <v>24.5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H25" t="n">
         <v>8.9</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="26">
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="H26" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G27" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="H28" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1727,7 +1727,7 @@
         <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0.5</v>
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.2</v>
+        <v>22.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2129,14 +2129,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>3.6</v>
       </c>
       <c r="G8" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H8" t="n">
         <v>5.2</v>
@@ -2249,23 +2249,23 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
@@ -2277,7 +2277,7 @@
         <v>0.8</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -2288,11 +2288,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2301,17 +2301,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I12" t="n">
         <v>1.6</v>
@@ -2320,7 +2320,7 @@
         <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -2331,30 +2331,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.8</v>
+        <v>23.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="H13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I13" t="n">
         <v>1.6</v>
@@ -2363,7 +2363,7 @@
         <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.2</v>
+        <v>22.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G14" t="n">
         <v>6.4</v>
       </c>
       <c r="H14" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="I14" t="n">
         <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="16">
@@ -2464,20 +2464,20 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
         <v>6.8</v>
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2</v>
+        <v>7.1</v>
       </c>
       <c r="H18" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="19">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2597,31 +2597,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
         <v>6.5</v>
       </c>
       <c r="H19" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.1</v>
+        <v>23.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H21" t="n">
         <v>5.2</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="22">
@@ -2722,16 +2722,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G23" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H23" t="n">
         <v>5.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G24" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="H24" t="n">
         <v>5.4</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.2</v>
+        <v>23.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="G25" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H25" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.6</v>
+        <v>25.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G26" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H26" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="27">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.1</v>
+        <v>24.7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="29">
@@ -3019,39 +3019,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.7</v>
+        <v>24.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G29" t="n">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="H29" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K29" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="30">
@@ -3066,16 +3066,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -3109,16 +3109,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -3137,7 +3137,7 @@
         <v>0.8</v>
       </c>
       <c r="K31" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3337,7 +3337,7 @@
         <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
@@ -3348,27 +3348,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.2</v>
+        <v>21</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="H5" t="n">
         <v>4.5</v>
@@ -3377,10 +3377,10 @@
         <v>1.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.9</v>
+        <v>22.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G6" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="H6" t="n">
         <v>4.5</v>
@@ -3420,10 +3420,10 @@
         <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="7">
@@ -3438,23 +3438,23 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G7" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="H7" t="n">
         <v>3.4</v>
@@ -3463,7 +3463,7 @@
         <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
         <v>2.9</v>
@@ -3485,12 +3485,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -3520,36 +3520,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="n">
         <v>2.3</v>
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
         <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.2</v>
+        <v>20.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20.5</v>
+        <v>21.2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -3735,36 +3735,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K14" t="n">
         <v>2.3</v>
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.5</v>
+        <v>23.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G15" t="n">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="16">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G16" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="n">
         <v>8.4</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18">
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G18" t="n">
         <v>7.8</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I18" t="n">
         <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -3950,11 +3950,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3963,26 +3963,26 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G19" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4019,7 +4019,7 @@
         <v>5.1</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0.8</v>
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.9</v>
+        <v>23.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G22" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H22" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
         <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="23">
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.2</v>
+        <v>23.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G23" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H23" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="I23" t="n">
         <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.2</v>
+        <v>23.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2.7</v>
       </c>
       <c r="G24" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="25">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>2.7</v>
       </c>
       <c r="G25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H25" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="26">
@@ -4255,29 +4255,29 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="H26" t="n">
         <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0.7</v>
@@ -4345,22 +4345,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>2.9</v>
       </c>
       <c r="G28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
         <v>1.8</v>
@@ -4369,7 +4369,7 @@
         <v>0.8</v>
       </c>
       <c r="K28" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="29">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4403,10 +4403,10 @@
         <v>7.4</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -4427,23 +4427,23 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G30" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H30" t="n">
         <v>4.7</v>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4600,10 +4600,10 @@
         <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -4640,10 +4640,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G3" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -4713,20 +4713,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="n">
         <v>9.300000000000001</v>
@@ -4738,7 +4738,7 @@
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="n">
         <v>2.3</v>
@@ -4795,36 +4795,36 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>21.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>10.3</v>
+        <v>10.8</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K7" t="n">
         <v>2.9</v>
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.4</v>
+        <v>22.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="H8" t="n">
         <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
         <v>1.2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.7</v>
+        <v>21</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G9" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J9" t="n">
         <v>1.3</v>
       </c>
-      <c r="J9" t="n">
-        <v>1.7</v>
-      </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="11">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="G12" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J12" t="n">
         <v>1.4</v>
       </c>
-      <c r="J12" t="n">
-        <v>1.8</v>
-      </c>
       <c r="K12" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.1</v>
+        <v>21.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="G13" t="n">
         <v>10.6</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G15" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="16">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.6</v>
+        <v>22.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.1</v>
+        <v>22.3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G18" t="n">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
       <c r="H18" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K19" t="n">
         <v>2.1</v>
-      </c>
-      <c r="G19" t="n">
-        <v>11</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>1.2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -5401,26 +5401,26 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
         <v>1.7</v>
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.4</v>
+        <v>22.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>9.6</v>
+        <v>10.3</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -5526,36 +5526,36 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G24" t="n">
-        <v>10.4</v>
+        <v>9.6</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K24" t="n">
         <v>2.5</v>
@@ -5569,15 +5569,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.8</v>
+        <v>23.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5586,22 +5586,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>9.699999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="H25" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K25" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22.6</v>
+        <v>24</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="G26" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="27">
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>22.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G27" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="28">
@@ -5702,23 +5702,23 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>2.6</v>
       </c>
       <c r="G28" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="H28" t="n">
         <v>4.2</v>
@@ -5831,20 +5831,20 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.9</v>
+        <v>26.2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G31" t="n">
         <v>10.5</v>
@@ -5941,39 +5941,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.5</v>
+        <v>18.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>13.3</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.5</v>
+        <v>19.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I3" t="n">
         <v>1.2</v>
       </c>
-      <c r="G3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1.7</v>
       </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.3</v>
+        <v>21.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G4" t="n">
-        <v>13.5</v>
+        <v>14.9</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -6070,30 +6070,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I5" t="n">
         <v>1.3</v>
@@ -6102,7 +6102,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.3</v>
+        <v>19.3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.8</v>
+        <v>19.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
         <v>1.5</v>
       </c>
-      <c r="G8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K8" t="n">
         <v>2.2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.9</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>13.2</v>
+        <v>14.4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>19.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="G10" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19.6</v>
+        <v>22</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18.7</v>
+        <v>19.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
         <v>13.9</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.7</v>
+        <v>22.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J13" t="n">
         <v>1.9</v>
       </c>
-      <c r="G13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.8</v>
-      </c>
       <c r="K13" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="14">
@@ -6457,36 +6457,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19.3</v>
+        <v>18.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G14" t="n">
-        <v>14.7</v>
+        <v>13.9</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="n">
         <v>2.9</v>
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.3</v>
+        <v>20.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G15" t="n">
-        <v>15.1</v>
+        <v>12.6</v>
       </c>
       <c r="H15" t="n">
         <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>12.6</v>
+        <v>15.8</v>
       </c>
       <c r="H16" t="n">
         <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="17">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -6594,31 +6594,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I17" t="n">
         <v>1.4</v>
       </c>
-      <c r="G17" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -6672,36 +6672,36 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.2</v>
+        <v>21.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="G19" t="n">
-        <v>15.3</v>
+        <v>13.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
         <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K19" t="n">
         <v>2.7</v>
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
         <v>1.3</v>
-      </c>
-      <c r="G20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>1.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.7</v>
+        <v>21.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G21" t="n">
         <v>14.5</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G22" t="n">
-        <v>15.8</v>
+        <v>14.1</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>1.9</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.6</v>
+        <v>22.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G23" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="H23" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="24">
@@ -6934,7 +6934,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -6943,26 +6943,26 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="H25" t="n">
         <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="26">
@@ -7063,23 +7063,23 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="H28" t="n">
         <v>3.6</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -497,39 +497,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -540,39 +540,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="4">
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.7</v>
+        <v>21.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.4</v>
       </c>
     </row>
     <row r="6">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.1</v>
+        <v>21.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H6" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.9</v>
+        <v>23</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H7" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -755,39 +755,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.6</v>
+        <v>23.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="G8" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="H8" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H9" t="n">
         <v>7.1</v>
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25.6</v>
+        <v>22.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H10" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.3</v>
+        <v>26.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G11" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="12">
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.9</v>
+        <v>25.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H12" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26.3</v>
+        <v>23</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -1013,36 +1013,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="H14" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
         <v>2.9</v>
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>24.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H15" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.2</v>
+        <v>23.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="G16" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H16" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -1142,36 +1142,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.8</v>
+        <v>24.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="H17" t="n">
         <v>8.4</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
         <v>3.6</v>
@@ -1185,36 +1185,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.7</v>
+        <v>23.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
         <v>8.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="n">
         <v>3.6</v>
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.7</v>
+        <v>23.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="H19" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="20">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.8</v>
+        <v>24.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="H21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="22">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.8</v>
+        <v>25.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="H23" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="24">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.8</v>
+        <v>24.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G24" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="H24" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K24" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="25">
@@ -1486,39 +1486,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="H25" t="n">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K25" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="26">
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.7</v>
+        <v>25.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="H26" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>24.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="G27" t="n">
         <v>6.9</v>
       </c>
       <c r="H27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>26.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G28" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="H28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="29">
@@ -1662,32 +1662,32 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G29" t="n">
         <v>5.7</v>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K29" t="n">
         <v>3</v>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1881,7 +1881,7 @@
         <v>6.5</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -1890,7 +1890,7 @@
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
@@ -1901,39 +1901,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.8</v>
+        <v>22.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1944,20 +1944,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.3</v>
+        <v>21.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1967,16 +1967,16 @@
         <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="H5" t="n">
         <v>5.3</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -2043,14 +2043,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H6" t="n">
         <v>5</v>
@@ -2062,7 +2062,7 @@
         <v>0.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2096,16 +2096,16 @@
         <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -2116,30 +2116,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I8" t="n">
         <v>1.6</v>
@@ -2148,7 +2148,7 @@
         <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G9" t="n">
         <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
         <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.4</v>
+        <v>22.5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="12">
@@ -2288,11 +2288,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2301,17 +2301,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I12" t="n">
         <v>1.6</v>
@@ -2320,7 +2320,7 @@
         <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>7.5</v>
+        <v>6.4</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
         <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="H14" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>6.1</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="n">
         <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2468,31 +2468,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G16" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H16" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.2</v>
+        <v>22.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K17" t="n">
         <v>2.8</v>
-      </c>
-      <c r="G17" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="H17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2.2</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.1</v>
+        <v>22.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>3.6</v>
       </c>
       <c r="G18" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="H18" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H19" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="I19" t="n">
         <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H20" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.4</v>
+        <v>23.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2</v>
+        <v>7.1</v>
       </c>
       <c r="H21" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -2765,11 +2765,11 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
         <v>6.5</v>
@@ -2793,7 +2793,7 @@
         <v>0.7</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.2</v>
+        <v>25.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G24" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H24" t="n">
         <v>5.4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -2855,16 +2855,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G25" t="n">
         <v>6.3</v>
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.2</v>
+        <v>23.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="G26" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H26" t="n">
         <v>5.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="27">
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.7</v>
+        <v>24.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="H28" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="29">
@@ -3019,39 +3019,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.1</v>
+        <v>25</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K29" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="30">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3348,27 +3348,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>22.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="H5" t="n">
         <v>4.5</v>
@@ -3377,10 +3377,10 @@
         <v>1.6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -3391,27 +3391,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.2</v>
+        <v>21</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="H6" t="n">
         <v>4.5</v>
@@ -3420,10 +3420,10 @@
         <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3457,7 +3457,7 @@
         <v>7.3</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
         <v>1.6</v>
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.7</v>
+        <v>20.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -3563,36 +3563,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
         <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K10" t="n">
         <v>2.3</v>
@@ -3606,27 +3606,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20.5</v>
+        <v>21.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
         <v>4.1</v>
@@ -3635,10 +3635,10 @@
         <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>8.4</v>
+        <v>6.7</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13">
@@ -3696,11 +3696,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3712,7 +3712,7 @@
         <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H13" t="n">
         <v>4.6</v>
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0.9</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -3782,16 +3782,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
         <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -3950,11 +3950,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3963,26 +3963,26 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.9</v>
+        <v>23.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H20" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
         <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="21">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.9</v>
+        <v>23.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G23" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H23" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I23" t="n">
         <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="24">
@@ -4173,22 +4173,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="H24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I24" t="n">
         <v>1.7</v>
@@ -4255,26 +4255,26 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.7</v>
+        <v>25.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I26" t="n">
         <v>1.8</v>
@@ -4298,16 +4298,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4337,39 +4337,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>2.9</v>
       </c>
       <c r="G28" t="n">
-        <v>8.699999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -4380,39 +4380,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23.4</v>
+        <v>24</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>2.9</v>
       </c>
       <c r="G29" t="n">
-        <v>7.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="30">
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4670,23 +4670,23 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1.9</v>
       </c>
       <c r="G4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H4" t="n">
         <v>3.6</v>
@@ -4695,7 +4695,7 @@
         <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K4" t="n">
         <v>2.1</v>
@@ -4756,16 +4756,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4775,13 +4775,13 @@
         <v>9.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
         <v>0.9</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
         <v>2.1</v>
@@ -4795,27 +4795,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.4</v>
+        <v>22.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -4827,7 +4827,7 @@
         <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.2</v>
+        <v>20.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="G8" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -4881,36 +4881,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K9" t="n">
         <v>2.9</v>
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.2</v>
+        <v>23.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="H11" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="I11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J11" t="n">
         <v>1.4</v>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>21.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="K12" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.5</v>
+        <v>22.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G13" t="n">
-        <v>10.6</v>
+        <v>9.5</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
         <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G14" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="H14" t="n">
         <v>4.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
         <v>1.1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="H15" t="n">
         <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>1.1</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -5248,7 +5248,7 @@
         <v>10.3</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="I17" t="n">
         <v>1.5</v>
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>1.2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="n">
-        <v>11.6</v>
+        <v>10.3</v>
       </c>
       <c r="H23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
         <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.4</v>
+        <v>22.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="G24" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="H24" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>1.2</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G26" t="n">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K26" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="27">
@@ -5659,16 +5659,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5684,7 +5684,7 @@
         <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K27" t="n">
         <v>2.9</v>
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.9</v>
+        <v>26.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5773,7 +5773,7 @@
         <v>1.3</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="30">
@@ -5788,20 +5788,20 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G30" t="n">
         <v>12.3</v>
@@ -5810,7 +5810,7 @@
         <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -5945,16 +5945,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -5988,11 +5988,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6001,10 +6001,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="H3" t="n">
         <v>3.6</v>
@@ -6027,30 +6027,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1.3</v>
       </c>
       <c r="G4" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
         <v>1.3</v>
@@ -6059,7 +6059,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5">
@@ -6070,30 +6070,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.2</v>
+        <v>21.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
         <v>1.3</v>
@@ -6102,7 +6102,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -6160,23 +6160,23 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="H7" t="n">
         <v>3</v>
@@ -6188,7 +6188,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.9</v>
+        <v>20.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.7</v>
+        <v>19.9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G9" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K9" t="n">
         <v>2.2</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -6289,7 +6289,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -6298,14 +6298,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>0.6</v>
       </c>
       <c r="G10" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="H10" t="n">
         <v>4</v>
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19.6</v>
+        <v>22.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G12" t="n">
-        <v>13.9</v>
+        <v>15.1</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>1.9</v>
       </c>
       <c r="K12" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I13" t="n">
         <v>1.3</v>
       </c>
-      <c r="G13" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.7</v>
-      </c>
       <c r="J13" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6461,11 +6461,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6504,11 +6504,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6520,7 +6520,7 @@
         <v>1.2</v>
       </c>
       <c r="G15" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="H15" t="n">
         <v>4.1</v>
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>1.9</v>
       </c>
       <c r="G17" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="H17" t="n">
         <v>3.9</v>
@@ -6629,30 +6629,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1.1</v>
       </c>
       <c r="G18" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
         <v>1.3</v>
@@ -6661,7 +6661,7 @@
         <v>1.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -6715,30 +6715,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1.1</v>
       </c>
       <c r="G20" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I20" t="n">
         <v>1.3</v>
@@ -6747,7 +6747,7 @@
         <v>1.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
@@ -6766,19 +6766,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G21" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="H21" t="n">
         <v>4.6</v>
@@ -6790,7 +6790,7 @@
         <v>1.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
@@ -6891,20 +6891,20 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="G24" t="n">
         <v>14.7</v>
@@ -6916,7 +6916,7 @@
         <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="K24" t="n">
         <v>3.2</v>
@@ -6934,16 +6934,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -7016,27 +7016,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22.9</v>
+        <v>24.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="G27" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="H27" t="n">
         <v>4.5</v>
@@ -7045,10 +7045,10 @@
         <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="K27" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="28">
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G28" t="n">
-        <v>14.3</v>
+        <v>14.7</v>
       </c>
       <c r="H28" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="29">
@@ -7102,39 +7102,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.4</v>
+        <v>22.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>14.8</v>
+        <v>14.3</v>
       </c>
       <c r="H29" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K29" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="30">
@@ -7149,7 +7149,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7158,23 +7158,23 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="H30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I30" t="n">
         <v>1.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="K30" t="n">
         <v>2.7</v>
@@ -7196,25 +7196,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1.2</v>
       </c>
       <c r="G31" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="H31" t="n">
         <v>4.3</v>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>2.3</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -497,39 +497,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
@@ -540,39 +540,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H3" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -596,14 +596,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="H4" t="n">
         <v>7.5</v>
@@ -615,7 +615,7 @@
         <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="5">
@@ -634,22 +634,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>2.7</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H5" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I5" t="n">
         <v>2.1</v>
@@ -658,7 +658,7 @@
         <v>0.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="H6" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="7">
@@ -755,39 +755,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.1</v>
+        <v>21.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H8" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26.3</v>
+        <v>23</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>26.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="14">
@@ -1064,22 +1064,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>1.9</v>
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.1</v>
+        <v>23.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.7</v>
+        <v>23.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H17" t="n">
-        <v>8.4</v>
+        <v>9.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1193,31 +1193,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="H18" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.8</v>
+        <v>24.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="H19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.8</v>
+        <v>24.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="H20" t="n">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="21">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.7</v>
+        <v>24.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="H21" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1767,7 +1767,7 @@
         <v>6.4</v>
       </c>
       <c r="H31" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>2.3</v>
@@ -1776,7 +1776,7 @@
         <v>0.7</v>
       </c>
       <c r="K31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.2</v>
+        <v>22.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
         <v>1.6</v>
@@ -2148,7 +2148,7 @@
         <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -2159,30 +2159,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
@@ -2191,7 +2191,7 @@
         <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.5</v>
+        <v>23.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G11" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="H11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="H12" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.2</v>
+        <v>22.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2382,31 +2382,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15">
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2430,14 +2430,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H15" t="n">
         <v>4.7</v>
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.6</v>
+        <v>23.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G17" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
         <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -2636,11 +2636,11 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2655,7 +2655,7 @@
         <v>6.5</v>
       </c>
       <c r="H20" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I20" t="n">
         <v>1.8</v>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -2750,7 +2750,7 @@
         <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2910,7 +2910,7 @@
         <v>3.5</v>
       </c>
       <c r="G26" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H26" t="n">
         <v>5.4</v>
@@ -2922,7 +2922,7 @@
         <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -2933,36 +2933,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.5</v>
+        <v>24.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>3.3</v>
       </c>
       <c r="G27" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="H27" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K27" t="n">
         <v>2.8</v>
@@ -2976,36 +2976,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.1</v>
+        <v>23.5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3.3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K28" t="n">
         <v>2.8</v>
@@ -3075,14 +3075,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="G30" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H30" t="n">
         <v>6.6</v>
@@ -3219,39 +3219,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
         <v>3.8</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="3">
@@ -3262,39 +3262,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.7</v>
+        <v>21</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4">
@@ -3305,39 +3305,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>22.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H4" t="n">
         <v>3.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>22.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
         <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.2</v>
+        <v>20.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2.7</v>
       </c>
       <c r="G7" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.5</v>
+        <v>21.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
         <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3563,36 +3563,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
         <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
         <v>2.3</v>
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.9</v>
+        <v>22.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.2</v>
+        <v>21.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="16">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G17" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18">
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.7</v>
+        <v>23.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G19" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.9</v>
+        <v>22.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4059,7 +4059,7 @@
         <v>7.7</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
         <v>1.6</v>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G23" t="n">
-        <v>7.6</v>
+        <v>8.9</v>
       </c>
       <c r="H23" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="I23" t="n">
         <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="24">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4173,31 +4173,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
       <c r="I24" t="n">
         <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="25">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.3</v>
+        <v>23.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
       <c r="H26" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.4</v>
+        <v>25.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>8.9</v>
+        <v>7.3</v>
       </c>
       <c r="H27" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28">
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>2.9</v>
       </c>
       <c r="G28" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="H28" t="n">
         <v>4.4</v>
@@ -4431,12 +4431,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -4584,23 +4584,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="H2" t="n">
         <v>3.9</v>
@@ -4612,7 +4612,7 @@
         <v>0.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="3">
@@ -4627,23 +4627,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>2.4</v>
       </c>
       <c r="G3" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.3</v>
+        <v>22.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K5" t="n">
         <v>2.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2.3</v>
       </c>
     </row>
     <row r="6">
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.5</v>
+        <v>20.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4928,11 +4928,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4944,10 +4944,10 @@
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I10" t="n">
         <v>1.3</v>
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G13" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.8</v>
+        <v>22.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="n">
-        <v>10.8</v>
+        <v>9.5</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
         <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G15" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="H15" t="n">
         <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
         <v>1.1</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="16">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
         <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G18" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I18" t="n">
         <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="19">
@@ -5319,19 +5319,19 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G19" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="H19" t="n">
         <v>4.2</v>
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.7</v>
+        <v>23</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="n">
-        <v>10.1</v>
+        <v>9.6</v>
       </c>
       <c r="H20" t="n">
         <v>4.3</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>1.1</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="21">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -5405,31 +5405,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G21" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>23.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="G23" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I23" t="n">
         <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="G24" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="H24" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
         <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.3</v>
+        <v>23.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>11.6</v>
+        <v>10.5</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>1.2</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>2.4</v>
       </c>
       <c r="G26" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>1.2</v>
       </c>
       <c r="K26" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="27">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -5730,7 +5730,7 @@
         <v>1.2</v>
       </c>
       <c r="K28" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="29">
@@ -5741,39 +5741,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.7</v>
+        <v>25</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G29" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="H29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1.9</v>
       </c>
     </row>
     <row r="30">
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="G30" t="n">
-        <v>12.3</v>
+        <v>10.9</v>
       </c>
       <c r="H30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K30" t="n">
         <v>1.9</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="31">
@@ -5831,26 +5831,26 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.2</v>
+        <v>25.9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>2.8</v>
       </c>
       <c r="G31" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="H31" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I31" t="n">
         <v>1.7</v>
@@ -5859,7 +5859,7 @@
         <v>1.6</v>
       </c>
       <c r="K31" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -6027,30 +6027,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.2</v>
+        <v>21.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1.3</v>
       </c>
       <c r="G4" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
         <v>1.3</v>
@@ -6059,7 +6059,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -6070,30 +6070,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I5" t="n">
         <v>1.3</v>
@@ -6102,7 +6102,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -6117,16 +6117,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -6136,10 +6136,10 @@
         <v>14.9</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
         <v>1.6</v>
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.7</v>
+        <v>19.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
         <v>1.5</v>
       </c>
-      <c r="G8" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K8" t="n">
         <v>2.2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G9" t="n">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.2</v>
+        <v>20.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
         <v>14.4</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
         <v>2.2</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -6336,22 +6336,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
         <v>1.1</v>
@@ -6375,16 +6375,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="G16" t="n">
-        <v>15.8</v>
+        <v>11.6</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J17" t="n">
         <v>1.9</v>
       </c>
-      <c r="G17" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.8</v>
-      </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="18">
@@ -6719,35 +6719,35 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1.1</v>
       </c>
       <c r="G20" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>1.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.6</v>
+        <v>22.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G22" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="H22" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G23" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="24">
@@ -7016,27 +7016,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.4</v>
+        <v>23.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="H27" t="n">
         <v>4.5</v>
@@ -7045,10 +7045,10 @@
         <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="28">
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.1</v>
+        <v>22.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="K28" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="29">
@@ -7102,39 +7102,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>22.4</v>
+        <v>24.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>14.3</v>
+        <v>14.8</v>
       </c>
       <c r="H29" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>2.1</v>
       </c>
       <c r="K29" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -563,7 +563,7 @@
         <v>5.7</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I3" t="n">
         <v>2.3</v>
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H5" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -669,36 +669,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="H6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
         <v>1.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
         <v>3.4</v>
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G7" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="8">
@@ -755,39 +755,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K8" t="n">
         <v>3.2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.7</v>
+        <v>26.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="G10" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H11" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -940,14 +940,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H12" t="n">
         <v>8.699999999999999</v>
@@ -959,7 +959,7 @@
         <v>0.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26.3</v>
+        <v>23.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="H13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="I13" t="n">
         <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.3</v>
+        <v>24.2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>7.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
         <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="16">
@@ -1099,30 +1099,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.8</v>
+        <v>22.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H16" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I16" t="n">
         <v>2.1</v>
@@ -1131,7 +1131,7 @@
         <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1146,35 +1146,35 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2.8</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H17" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
         <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -1189,11 +1189,11 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H19" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="H20" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="21">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.2</v>
+        <v>24.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G21" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="H21" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
         <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="22">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="H22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -1404,16 +1404,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1432,7 +1432,7 @@
         <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="24">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1469,13 +1469,13 @@
         <v>7.9</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0.5</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="25">
@@ -1486,39 +1486,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="H25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="26">
@@ -1529,36 +1529,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H26" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K26" t="n">
         <v>3</v>
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="H27" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="28">
@@ -1619,26 +1619,26 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>2.7</v>
       </c>
       <c r="G28" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I28" t="n">
         <v>2.1</v>
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.8</v>
+        <v>26.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="G29" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="H29" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0.5</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="30">
@@ -1701,39 +1701,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.2</v>
+        <v>24.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G30" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="H30" t="n">
         <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0.5</v>
       </c>
       <c r="K30" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1862,16 +1862,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1948,16 +1948,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1967,7 +1967,7 @@
         <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="n">
         <v>1.9</v>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2081,31 +2081,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
         <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -2163,16 +2163,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2182,7 +2182,7 @@
         <v>6.2</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
@@ -2191,7 +2191,7 @@
         <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2253,31 +2253,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H11" t="n">
-        <v>6</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.6</v>
+        <v>23.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="H12" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.5</v>
+        <v>23.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="H13" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -2374,33 +2374,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0.6</v>
@@ -2417,30 +2417,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.6</v>
+        <v>22.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="I15" t="n">
         <v>1.7</v>
@@ -2449,7 +2449,7 @@
         <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="16">
@@ -2460,27 +2460,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>3.4</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H16" t="n">
         <v>5.2</v>
@@ -2489,10 +2489,10 @@
         <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -2526,7 +2526,7 @@
         <v>6.9</v>
       </c>
       <c r="H17" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I17" t="n">
         <v>1.9</v>
@@ -2535,7 +2535,7 @@
         <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.9</v>
+        <v>23.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G18" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="H18" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G19" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="H19" t="n">
         <v>5.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G20" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="H20" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
@@ -2675,36 +2675,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G21" t="n">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="H21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K21" t="n">
         <v>2.9</v>
@@ -2718,30 +2718,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.1</v>
+        <v>25.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="G22" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H22" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
         <v>1.4</v>
@@ -2750,7 +2750,7 @@
         <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="23">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G23" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H23" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="24">
@@ -2804,24 +2804,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.2</v>
+        <v>23.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="G24" t="n">
         <v>6.7</v>
@@ -2830,13 +2830,13 @@
         <v>5.4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -2851,7 +2851,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H26" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="27">
@@ -2937,26 +2937,26 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="I27" t="n">
         <v>1.8</v>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2993,13 +2993,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G28" t="n">
         <v>6.7</v>
       </c>
       <c r="H28" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
         <v>1.9</v>
@@ -3019,39 +3019,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="G29" t="n">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="H29" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K29" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="30">
@@ -3062,39 +3062,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25.6</v>
+        <v>25.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="G30" t="n">
-        <v>6.9</v>
+        <v>7.7</v>
       </c>
       <c r="H30" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K30" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="31">
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G31" t="n">
         <v>7.1</v>
@@ -3137,7 +3137,7 @@
         <v>0.8</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -3223,11 +3223,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3239,10 +3239,10 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I2" t="n">
         <v>1.2</v>
@@ -3251,7 +3251,7 @@
         <v>0.7</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3">
@@ -3262,39 +3262,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>22.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H3" t="n">
         <v>3.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="4">
@@ -3305,24 +3305,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.1</v>
+        <v>20.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
         <v>7.8</v>
@@ -3331,13 +3331,13 @@
         <v>3.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
@@ -3352,7 +3352,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="H5" t="n">
         <v>4.5</v>
@@ -3395,16 +3395,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -3414,7 +3414,7 @@
         <v>7.3</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
         <v>1.6</v>
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.5</v>
+        <v>21.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
         <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.5</v>
+        <v>20.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -3571,31 +3571,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K10" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.9</v>
+        <v>21.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.4</v>
+        <v>21.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13">
@@ -3692,36 +3692,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
         <v>2.3</v>
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.2</v>
+        <v>23.2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G14" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="I14" t="n">
         <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.4</v>
+        <v>22.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G15" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.7</v>
+        <v>21.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
         <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="17">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G17" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.9</v>
+        <v>22.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.7</v>
+        <v>23.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="21">
@@ -4036,11 +4036,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.8</v>
+        <v>22.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4049,26 +4049,26 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G21" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22">
@@ -4079,11 +4079,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4092,17 +4092,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="G22" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H22" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="I22" t="n">
         <v>1.6</v>
@@ -4111,7 +4111,7 @@
         <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -4126,26 +4126,26 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>2.6</v>
       </c>
       <c r="G23" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I23" t="n">
         <v>1.7</v>
@@ -4154,7 +4154,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="24">
@@ -4212,16 +4212,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4234,13 +4234,13 @@
         <v>4.7</v>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0.9</v>
       </c>
       <c r="K25" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -4255,11 +4255,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4271,10 +4271,10 @@
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I26" t="n">
         <v>1.9</v>
@@ -4298,23 +4298,23 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="H27" t="n">
         <v>4.2</v>
@@ -4341,11 +4341,11 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G28" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="H28" t="n">
         <v>4.4</v>
@@ -4384,23 +4384,23 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>2.9</v>
       </c>
       <c r="G29" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H29" t="n">
         <v>4.5</v>
@@ -4431,19 +4431,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>2.9</v>
       </c>
       <c r="G30" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H30" t="n">
         <v>4.7</v>
@@ -4470,26 +4470,26 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3.3</v>
       </c>
       <c r="G31" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
@@ -4627,23 +4627,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>2.4</v>
       </c>
       <c r="G3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -4655,7 +4655,7 @@
         <v>1.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -4670,7 +4670,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4695,7 +4695,7 @@
         <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
         <v>2.1</v>
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.5</v>
+        <v>20.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.6</v>
+        <v>22.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G6" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
         <v>1.2</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J7" t="n">
         <v>1.3</v>
       </c>
-      <c r="J7" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K7" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>10.3</v>
+        <v>9.6</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9">
@@ -4885,29 +4885,29 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.2</v>
+        <v>21.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G9" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="H9" t="n">
         <v>4.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>1.2</v>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4956,7 +4956,7 @@
         <v>1.7</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="11">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>1.7</v>
       </c>
       <c r="G11" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H11" t="n">
         <v>3.7</v>
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.4</v>
+        <v>22.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>10.6</v>
+        <v>9.5</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
         <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.6</v>
+        <v>21.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G13" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -5143,11 +5143,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5159,10 +5159,10 @@
         <v>2.4</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
         <v>1.4</v>
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.3</v>
+        <v>23.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.6</v>
+        <v>22.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G19" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="G20" t="n">
-        <v>9.6</v>
+        <v>10.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.7</v>
+        <v>22.4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G23" t="n">
-        <v>9.5</v>
+        <v>10.1</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="G24" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="K24" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.9</v>
+        <v>22.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G25" t="n">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K25" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="26">
@@ -5616,11 +5616,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G26" t="n">
         <v>11.6</v>
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22.9</v>
+        <v>24.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G27" t="n">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="H27" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K27" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="28">
@@ -5702,20 +5702,20 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G28" t="n">
         <v>10.8</v>
@@ -5741,39 +5741,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25</v>
+        <v>26.6</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="G29" t="n">
-        <v>12.3</v>
+        <v>10.9</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K29" t="n">
         <v>1.9</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="30">
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.7</v>
+        <v>25</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="G30" t="n">
-        <v>10.9</v>
+        <v>12.3</v>
       </c>
       <c r="H30" t="n">
         <v>4.4</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31">
@@ -5941,39 +5941,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G2" t="n">
-        <v>13.3</v>
+        <v>14.9</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.2</v>
+        <v>18.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4">
@@ -6027,15 +6027,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.6</v>
+        <v>19.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6044,22 +6044,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>13.4</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5">
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.6</v>
+        <v>21.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
         <v>14.9</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
         <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -6164,22 +6164,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
         <v>1.2</v>
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.9</v>
+        <v>20.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.2</v>
+        <v>22</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>14.4</v>
+        <v>13.7</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
         <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.8</v>
+        <v>19.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" t="n">
         <v>1.5</v>
       </c>
-      <c r="G10" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K10" t="n">
         <v>2.2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="G11" t="n">
-        <v>13.7</v>
+        <v>14.4</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>15.1</v>
+        <v>13.7</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J12" t="n">
         <v>1.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>18.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="G13" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>1.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18.7</v>
+        <v>22</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="G14" t="n">
-        <v>13.9</v>
+        <v>15.1</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="15">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J16" t="n">
         <v>1.9</v>
       </c>
-      <c r="G16" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="K16" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="G17" t="n">
-        <v>15.8</v>
+        <v>11.8</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>1.9</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="G18" t="n">
-        <v>15.2</v>
+        <v>13.8</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
         <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="19">
@@ -6672,36 +6672,36 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="G19" t="n">
-        <v>13.7</v>
+        <v>15.2</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
         <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K19" t="n">
         <v>2.7</v>
@@ -6719,16 +6719,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -6741,7 +6741,7 @@
         <v>4.4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>1.8</v>
@@ -6762,26 +6762,26 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1.2</v>
       </c>
       <c r="G21" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I21" t="n">
         <v>1.4</v>
@@ -6891,16 +6891,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -6934,20 +6934,20 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G25" t="n">
         <v>15.4</v>
@@ -6959,7 +6959,7 @@
         <v>1.1</v>
       </c>
       <c r="J25" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K25" t="n">
         <v>2.7</v>
@@ -7024,31 +7024,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="H27" t="n">
         <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="28">
@@ -7063,23 +7063,23 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="H28" t="n">
         <v>3.6</v>
@@ -7091,7 +7091,7 @@
         <v>2.1</v>
       </c>
       <c r="K28" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="29">
@@ -7106,16 +7106,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -7125,7 +7125,7 @@
         <v>14.8</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
         <v>1.6</v>
@@ -7149,32 +7149,32 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.8</v>
+        <v>26</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G30" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="H30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I30" t="n">
         <v>1.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="K30" t="n">
         <v>2.7</v>
@@ -7192,11 +7192,11 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>58.8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -497,39 +497,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H2" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -540,39 +540,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
@@ -673,23 +673,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -845,11 +845,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26.3</v>
+        <v>26.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.7</v>
+        <v>23.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H12" t="n">
-        <v>8.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.3</v>
+        <v>24.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>7.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.2</v>
+        <v>25.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="H14" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>1.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.8</v>
+        <v>22.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H15" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
         <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.7</v>
+        <v>23.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="17">
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="H21" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.2</v>
+        <v>25.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H22" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="I22" t="n">
         <v>1.9</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25.8</v>
+        <v>24.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G23" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="H23" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.1</v>
+        <v>25.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G29" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="H29" t="n">
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0.5</v>
       </c>
       <c r="K29" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1701,39 +1701,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.9</v>
+        <v>26.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G30" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="H30" t="n">
         <v>9</v>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0.5</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="31">
@@ -1748,16 +1748,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1767,7 +1767,7 @@
         <v>6.4</v>
       </c>
       <c r="H31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I31" t="n">
         <v>2.3</v>
@@ -1776,7 +1776,7 @@
         <v>0.7</v>
       </c>
       <c r="K31" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>
@@ -1901,39 +1901,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.6</v>
+        <v>22</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="4">
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>23.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.2</v>
+        <v>22.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H8" t="n">
         <v>5.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.8</v>
+        <v>22.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>84.1</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
         <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2253,31 +2253,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H11" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.2</v>
+        <v>22.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.6</v>
+        <v>23.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H15" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="16">
@@ -2464,23 +2464,23 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>3.4</v>
       </c>
       <c r="G16" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="H16" t="n">
         <v>5.2</v>
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G17" t="n">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="H17" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2597,31 +2597,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="H19" t="n">
         <v>5.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="20">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -2640,31 +2640,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G20" t="n">
-        <v>6.3</v>
+        <v>7.2</v>
       </c>
       <c r="H20" t="n">
         <v>5.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -2718,30 +2718,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>25.2</v>
+        <v>24.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="G22" t="n">
         <v>6.7</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="I22" t="n">
         <v>1.4</v>
@@ -2750,7 +2750,7 @@
         <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.2</v>
+        <v>23.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G23" t="n">
         <v>6.7</v>
       </c>
       <c r="H23" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.2</v>
+        <v>25.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G24" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H24" t="n">
         <v>5.4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="G25" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="H25" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G26" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="H26" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="27">
@@ -2941,22 +2941,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G27" t="n">
         <v>7.1</v>
       </c>
       <c r="H27" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
         <v>1.8</v>
@@ -3023,16 +3023,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -3266,32 +3266,32 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>1.3</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K3" t="n">
         <v>2.6</v>
@@ -3309,26 +3309,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>1.7</v>
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.4</v>
+        <v>21.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.1</v>
+        <v>21.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="n">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
@@ -3485,16 +3485,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
         <v>7.6</v>
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.4</v>
+        <v>22.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.9</v>
+        <v>21.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -3653,23 +3653,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="H12" t="n">
         <v>4.1</v>
@@ -3696,11 +3696,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.2</v>
+        <v>22.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G17" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3963,23 +3963,23 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K19" t="n">
         <v>2.6</v>
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.9</v>
+        <v>22.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -4036,39 +4036,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -4079,15 +4079,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.8</v>
+        <v>23</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4096,22 +4096,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>7.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="23">
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>22.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H23" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="24">
@@ -4169,16 +4169,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4188,7 +4188,7 @@
         <v>7.7</v>
       </c>
       <c r="H24" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I24" t="n">
         <v>1.7</v>
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.1</v>
+        <v>23.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="H25" t="n">
         <v>4.7</v>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0.9</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="26">
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4689,16 +4689,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I4" t="n">
         <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -4732,13 +4732,13 @@
         <v>9.300000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="n">
         <v>2.4</v>
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J6" t="n">
         <v>1.3</v>
       </c>
-      <c r="J6" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K6" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.1</v>
+        <v>22.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="G7" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.9</v>
+        <v>21.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K8" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.1</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4932,31 +4932,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
         <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4975,31 +4975,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
         <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="12">
@@ -5010,11 +5010,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.4</v>
+        <v>21.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5023,26 +5023,26 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
         <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K12" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.4</v>
+        <v>22.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G13" t="n">
-        <v>10.6</v>
+        <v>9.5</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
         <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -5100,16 +5100,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G15" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="16">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G17" t="n">
-        <v>10.2</v>
+        <v>10.7</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J21" t="n">
         <v>1.6</v>
       </c>
-      <c r="J21" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K21" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="G22" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         <v>2.2</v>
       </c>
       <c r="G23" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="H23" t="n">
         <v>4.3</v>
@@ -5534,12 +5534,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -5831,32 +5831,32 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G31" t="n">
         <v>10.4</v>
       </c>
       <c r="H31" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I31" t="n">
         <v>1.7</v>
       </c>
       <c r="J31" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
@@ -5941,39 +5941,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.6</v>
+        <v>18.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>14.9</v>
+        <v>13.3</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.6</v>
+        <v>19.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I3" t="n">
         <v>1.2</v>
       </c>
-      <c r="G3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1.7</v>
       </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="4">
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.2</v>
+        <v>21.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G4" t="n">
-        <v>13.4</v>
+        <v>15.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5">
@@ -6070,30 +6070,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
         <v>1.3</v>
@@ -6102,7 +6102,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.7</v>
+        <v>19.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
         <v>14.9</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.6</v>
+        <v>20.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I7" t="n">
         <v>1.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.8</v>
+        <v>19.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
         <v>1.2</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G9" t="n">
-        <v>13.7</v>
+        <v>15.1</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.9</v>
+        <v>21.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J10" t="n">
         <v>1.5</v>
       </c>
-      <c r="J10" t="n">
-        <v>1.4</v>
-      </c>
       <c r="K10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="H11" t="n">
         <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K11" t="n">
         <v>2.2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -6375,16 +6375,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18.6</v>
+        <v>19.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G13" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22</v>
+        <v>18.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="G14" t="n">
-        <v>15.1</v>
+        <v>13.9</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="G15" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -6594,31 +6594,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="G17" t="n">
-        <v>11.8</v>
+        <v>13.7</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="18">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -6637,31 +6637,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I18" t="n">
         <v>1.4</v>
       </c>
-      <c r="G18" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J18" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
@@ -6672,30 +6672,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1.1</v>
       </c>
       <c r="G19" t="n">
-        <v>15.2</v>
+        <v>15.6</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I19" t="n">
         <v>1.3</v>
@@ -6704,7 +6704,7 @@
         <v>1.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -6715,30 +6715,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20.9</v>
+        <v>21.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1.1</v>
       </c>
       <c r="G20" t="n">
-        <v>15.6</v>
+        <v>15.2</v>
       </c>
       <c r="H20" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
         <v>1.3</v>
@@ -6747,7 +6747,7 @@
         <v>1.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -6758,33 +6758,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>1.2</v>
       </c>
       <c r="G21" t="n">
-        <v>14.2</v>
+        <v>12.6</v>
       </c>
       <c r="H21" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>1.8</v>
@@ -6821,7 +6821,7 @@
         <v>1.4</v>
       </c>
       <c r="G22" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="H22" t="n">
         <v>4</v>
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.5</v>
+        <v>25.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="G23" t="n">
-        <v>14.1</v>
+        <v>14.7</v>
       </c>
       <c r="H23" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.1</v>
+        <v>21.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="G24" t="n">
-        <v>14.7</v>
+        <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="25">
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>1.2</v>
       </c>
       <c r="G26" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="H26" t="n">
         <v>4</v>
@@ -7192,11 +7192,11 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>58.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
